--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_700.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_700.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C157"/>
+  <dimension ref="A1:C132"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,32 +396,32 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>121</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>122</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C4">
         <v>7</v>
@@ -429,57 +429,57 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="B5">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>86</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>19</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>232</v>
+        <v>642</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>172</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -490,444 +490,444 @@
         <v>2</v>
       </c>
       <c r="C10">
-        <v>173</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>402</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>159</v>
+        <v>220</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12">
-        <v>806</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>201</v>
+        <v>308</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13">
-        <v>349</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>206</v>
+        <v>334</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>221</v>
+        <v>335</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15">
-        <v>58</v>
+        <v>735</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>248</v>
+        <v>336</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C16">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>286</v>
+        <v>344</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C17">
-        <v>156</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>305</v>
+        <v>354</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>308</v>
+        <v>361</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>7</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>332</v>
+        <v>515</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C20">
-        <v>7</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>336</v>
+        <v>523</v>
       </c>
       <c r="B21">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>124</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>344</v>
+        <v>590</v>
       </c>
       <c r="B22">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C22">
-        <v>7</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>361</v>
+        <v>947</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C23">
-        <v>171</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>380</v>
+        <v>949</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C24">
-        <v>69</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>424</v>
+        <v>952</v>
       </c>
       <c r="B25">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C25">
-        <v>617</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>434</v>
+        <v>974</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26">
-        <v>113</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>435</v>
+        <v>990</v>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
       <c r="C27">
-        <v>113</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>436</v>
+        <v>995</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
       <c r="C28">
-        <v>113</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>590</v>
+        <v>996</v>
       </c>
       <c r="B29">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C29">
-        <v>109</v>
+        <v>260</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>944</v>
+        <v>1413</v>
       </c>
       <c r="B30">
         <v>15</v>
       </c>
       <c r="C30">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>947</v>
+        <v>1414</v>
       </c>
       <c r="B31">
         <v>15</v>
       </c>
       <c r="C31">
-        <v>46</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>990</v>
+        <v>1777</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>996</v>
+        <v>1895</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C33">
-        <v>7</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1055</v>
+        <v>2054</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34">
-        <v>41</v>
+        <v>267</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1065</v>
+        <v>2055</v>
       </c>
       <c r="B35">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C35">
-        <v>650</v>
+        <v>264</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1309</v>
+        <v>2057</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C36">
-        <v>61</v>
+        <v>264</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1409</v>
+        <v>2160</v>
       </c>
       <c r="B37">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="C37">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1765</v>
+        <v>2328</v>
       </c>
       <c r="B38">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C38">
-        <v>213</v>
+        <v>147</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>1766</v>
+        <v>2423</v>
       </c>
       <c r="B39">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="C39">
-        <v>211</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>1767</v>
+        <v>2438</v>
       </c>
       <c r="B40">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>197</v>
+        <v>368</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>1801</v>
+        <v>2744</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C41">
-        <v>112</v>
+        <v>200</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>1880</v>
+        <v>2774</v>
       </c>
       <c r="B42">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C42">
-        <v>247</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2049</v>
+        <v>2934</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C43">
-        <v>610</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2054</v>
+        <v>3016</v>
       </c>
       <c r="B44">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C44">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2308</v>
+        <v>3059</v>
       </c>
       <c r="B45">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C45">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2538</v>
+        <v>3477</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2729</v>
+        <v>3495</v>
       </c>
       <c r="B47">
         <v>3</v>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>590</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2734</v>
+        <v>4176</v>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C48">
-        <v>7</v>
+        <v>548</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2859</v>
+        <v>4372</v>
       </c>
       <c r="B49">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C49">
-        <v>80</v>
+        <v>617</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>3016</v>
+        <v>4883</v>
       </c>
       <c r="B50">
-        <v>68</v>
+        <v>332</v>
       </c>
       <c r="C50">
         <v>7</v>
@@ -935,54 +935,54 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>3047</v>
+        <v>5007</v>
       </c>
       <c r="B51">
         <v>3</v>
       </c>
       <c r="C51">
-        <v>297</v>
+        <v>897</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>3048</v>
+        <v>5081</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C52">
-        <v>7</v>
+        <v>211</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>3429</v>
+        <v>5086</v>
       </c>
       <c r="B53">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C53">
-        <v>61</v>
+        <v>325</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>3430</v>
+        <v>5208</v>
       </c>
       <c r="B54">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C54">
-        <v>80</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3454</v>
+        <v>5341</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C55">
         <v>7</v>
@@ -990,406 +990,406 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3462</v>
+        <v>5490</v>
       </c>
       <c r="B56">
         <v>2</v>
       </c>
       <c r="C56">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3840</v>
+        <v>5494</v>
       </c>
       <c r="B57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57">
-        <v>192</v>
+        <v>57</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3889</v>
+        <v>5584</v>
       </c>
       <c r="B58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C58">
-        <v>7</v>
+        <v>319</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3891</v>
+        <v>5722</v>
       </c>
       <c r="B59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C59">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3899</v>
+        <v>5723</v>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C60">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>4223</v>
+        <v>6575</v>
       </c>
       <c r="B61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C61">
-        <v>48</v>
+        <v>144</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>4224</v>
+        <v>7324</v>
       </c>
       <c r="B62">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C62">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>4232</v>
+        <v>8059</v>
       </c>
       <c r="B63">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C63">
-        <v>7</v>
+        <v>378</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>4899</v>
+        <v>8104</v>
       </c>
       <c r="B64">
-        <v>332</v>
+        <v>1</v>
       </c>
       <c r="C64">
-        <v>8</v>
+        <v>114</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>4962</v>
+        <v>8216</v>
       </c>
       <c r="B65">
-        <v>332</v>
+        <v>10</v>
       </c>
       <c r="C65">
-        <v>42</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5127</v>
+        <v>8286</v>
       </c>
       <c r="B66">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C66">
-        <v>8</v>
+        <v>274</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5153</v>
+        <v>8676</v>
       </c>
       <c r="B67">
         <v>2</v>
       </c>
       <c r="C67">
-        <v>27</v>
+        <v>162</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5208</v>
+        <v>8753</v>
       </c>
       <c r="B68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C68">
-        <v>631</v>
+        <v>200</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5243</v>
+        <v>8853</v>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C69">
-        <v>279</v>
+        <v>324</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5341</v>
+        <v>8898</v>
       </c>
       <c r="B70">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C70">
-        <v>7</v>
+        <v>455</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5453</v>
+        <v>8915</v>
       </c>
       <c r="B71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C71">
-        <v>7</v>
+        <v>89</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5490</v>
+        <v>8938</v>
       </c>
       <c r="B72">
         <v>2</v>
       </c>
       <c r="C72">
-        <v>117</v>
+        <v>89</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5585</v>
+        <v>9786</v>
       </c>
       <c r="B73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C73">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5723</v>
+        <v>9787</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C74">
-        <v>68</v>
+        <v>41</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>5946</v>
+        <v>10406</v>
       </c>
       <c r="B75">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C75">
-        <v>7</v>
+        <v>935</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>5966</v>
+        <v>10524</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C76">
-        <v>8</v>
+        <v>31</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>6098</v>
+        <v>10616</v>
       </c>
       <c r="B77">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>84</v>
+        <v>48</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>6158</v>
+        <v>10716</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C78">
-        <v>10</v>
+        <v>58</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>6575</v>
+        <v>10906</v>
       </c>
       <c r="B79">
         <v>3</v>
       </c>
       <c r="C79">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>6965</v>
+        <v>10936</v>
       </c>
       <c r="B80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C80">
-        <v>42</v>
+        <v>80</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>7520</v>
+        <v>10994</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>7886</v>
+        <v>11089</v>
       </c>
       <c r="B82">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C82">
-        <v>160</v>
+        <v>127</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>8217</v>
+        <v>11090</v>
       </c>
       <c r="B83">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C83">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>8674</v>
+        <v>11092</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>315</v>
+        <v>47</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>8898</v>
+        <v>11159</v>
       </c>
       <c r="B85">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>7</v>
+        <v>277</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>8938</v>
+        <v>11234</v>
       </c>
       <c r="B86">
         <v>2</v>
       </c>
       <c r="C86">
-        <v>7</v>
+        <v>104</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>8939</v>
+        <v>11510</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C87">
-        <v>177</v>
+        <v>337</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>8944</v>
+        <v>11526</v>
       </c>
       <c r="B88">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C88">
-        <v>7</v>
+        <v>884</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>9065</v>
+        <v>11583</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C89">
-        <v>349</v>
+        <v>42</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>9070</v>
+        <v>11610</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C90">
-        <v>37</v>
+        <v>84</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>9081</v>
+        <v>11611</v>
       </c>
       <c r="B91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C91">
-        <v>14</v>
+        <v>78</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>9135</v>
+        <v>11684</v>
       </c>
       <c r="B92">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C92">
         <v>7</v>
@@ -1397,164 +1397,164 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>9208</v>
+        <v>11706</v>
       </c>
       <c r="B93">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C93">
-        <v>112</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>9507</v>
+        <v>11710</v>
       </c>
       <c r="B94">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C94">
-        <v>7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>9783</v>
+        <v>11813</v>
       </c>
       <c r="B95">
         <v>1</v>
       </c>
       <c r="C95">
-        <v>71</v>
+        <v>179</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>9784</v>
+        <v>11855</v>
       </c>
       <c r="B96">
         <v>1</v>
       </c>
       <c r="C96">
-        <v>76</v>
+        <v>58</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>9803</v>
+        <v>11858</v>
       </c>
       <c r="B97">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C97">
-        <v>827</v>
+        <v>58</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>9828</v>
+        <v>11886</v>
       </c>
       <c r="B98">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C98">
-        <v>7</v>
+        <v>110</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>10149</v>
+        <v>11895</v>
       </c>
       <c r="B99">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C99">
-        <v>1062</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>10275</v>
+        <v>11952</v>
       </c>
       <c r="B100">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C100">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>10407</v>
+        <v>12241</v>
       </c>
       <c r="B101">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C101">
-        <v>1293</v>
+        <v>255</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>10530</v>
+        <v>12351</v>
       </c>
       <c r="B102">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C102">
-        <v>7</v>
+        <v>723</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>10616</v>
+        <v>12352</v>
       </c>
       <c r="B103">
         <v>1</v>
       </c>
       <c r="C103">
-        <v>7</v>
+        <v>723</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>10825</v>
+        <v>12417</v>
       </c>
       <c r="B104">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C104">
-        <v>13</v>
+        <v>91</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>10993</v>
+        <v>12501</v>
       </c>
       <c r="B105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C105">
-        <v>60</v>
+        <v>176</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11059</v>
+        <v>12536</v>
       </c>
       <c r="B106">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C106">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11081</v>
+        <v>12539</v>
       </c>
       <c r="B107">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C107">
         <v>7</v>
@@ -1562,186 +1562,186 @@
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11090</v>
+        <v>12887</v>
       </c>
       <c r="B108">
         <v>1</v>
       </c>
       <c r="C108">
-        <v>7</v>
+        <v>387</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11091</v>
+        <v>12924</v>
       </c>
       <c r="B109">
         <v>1</v>
       </c>
       <c r="C109">
-        <v>91</v>
+        <v>29</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11092</v>
+        <v>12993</v>
       </c>
       <c r="B110">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C110">
-        <v>90</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11116</v>
+        <v>13034</v>
       </c>
       <c r="B111">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C111">
-        <v>90</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11180</v>
+        <v>13249</v>
       </c>
       <c r="B112">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C112">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11357</v>
+        <v>13880</v>
       </c>
       <c r="B113">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C113">
-        <v>7</v>
+        <v>252</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11396</v>
+        <v>13885</v>
       </c>
       <c r="B114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C114">
-        <v>7</v>
+        <v>130</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11467</v>
+        <v>14038</v>
       </c>
       <c r="B115">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C115">
-        <v>7</v>
+        <v>159</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11582</v>
+        <v>20927</v>
       </c>
       <c r="B116">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C116">
-        <v>57</v>
+        <v>45</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>11583</v>
+        <v>21704</v>
       </c>
       <c r="B117">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C117">
-        <v>7</v>
+        <v>884</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>11587</v>
+        <v>22313</v>
       </c>
       <c r="B118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C118">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>11610</v>
+        <v>22565</v>
       </c>
       <c r="B119">
         <v>3</v>
       </c>
       <c r="C119">
-        <v>167</v>
+        <v>661</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>11611</v>
+        <v>22920</v>
       </c>
       <c r="B120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C120">
-        <v>153</v>
+        <v>91</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>11689</v>
+        <v>23262</v>
       </c>
       <c r="B121">
         <v>2</v>
       </c>
       <c r="C121">
-        <v>345</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>11711</v>
+        <v>23563</v>
       </c>
       <c r="B122">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C122">
-        <v>234</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>11739</v>
+        <v>23611</v>
       </c>
       <c r="B123">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C123">
-        <v>66</v>
+        <v>257</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>11772</v>
+        <v>23878</v>
       </c>
       <c r="B124">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C124">
         <v>7</v>
@@ -1749,365 +1749,90 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>11846</v>
+        <v>24120</v>
       </c>
       <c r="B125">
         <v>3</v>
       </c>
       <c r="C125">
-        <v>7</v>
+        <v>356</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>11856</v>
+        <v>24252</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>11857</v>
+        <v>24257</v>
       </c>
       <c r="B127">
         <v>1</v>
       </c>
       <c r="C127">
-        <v>116</v>
+        <v>80</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>11858</v>
+        <v>24260</v>
       </c>
       <c r="B128">
         <v>1</v>
       </c>
       <c r="C128">
-        <v>114</v>
+        <v>82</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>11868</v>
+        <v>24566</v>
       </c>
       <c r="B129">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C129">
-        <v>7</v>
+        <v>175</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>11886</v>
+        <v>24707</v>
       </c>
       <c r="B130">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C130">
-        <v>220</v>
+        <v>689</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>11919</v>
+        <v>24889</v>
       </c>
       <c r="B131">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C131">
-        <v>170</v>
+        <v>134</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>12059</v>
+        <v>25958</v>
       </c>
       <c r="B132">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C132">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3">
-      <c r="A133">
-        <v>12128</v>
-      </c>
-      <c r="B133">
-        <v>1</v>
-      </c>
-      <c r="C133">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3">
-      <c r="A134">
-        <v>12611</v>
-      </c>
-      <c r="B134">
-        <v>1</v>
-      </c>
-      <c r="C134">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3">
-      <c r="A135">
-        <v>12887</v>
-      </c>
-      <c r="B135">
-        <v>1</v>
-      </c>
-      <c r="C135">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3">
-      <c r="A136">
-        <v>12924</v>
-      </c>
-      <c r="B136">
-        <v>1</v>
-      </c>
-      <c r="C136">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3">
-      <c r="A137">
-        <v>13023</v>
-      </c>
-      <c r="B137">
-        <v>3</v>
-      </c>
-      <c r="C137">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3">
-      <c r="A138">
-        <v>13258</v>
-      </c>
-      <c r="B138">
-        <v>29</v>
-      </c>
-      <c r="C138">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3">
-      <c r="A139">
-        <v>13299</v>
-      </c>
-      <c r="B139">
-        <v>1</v>
-      </c>
-      <c r="C139">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3">
-      <c r="A140">
-        <v>19987</v>
-      </c>
-      <c r="B140">
-        <v>2</v>
-      </c>
-      <c r="C140">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3">
-      <c r="A141">
-        <v>20977</v>
-      </c>
-      <c r="B141">
-        <v>1</v>
-      </c>
-      <c r="C141">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3">
-      <c r="A142">
-        <v>21712</v>
-      </c>
-      <c r="B142">
-        <v>3</v>
-      </c>
-      <c r="C142">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3">
-      <c r="A143">
-        <v>21793</v>
-      </c>
-      <c r="B143">
-        <v>1</v>
-      </c>
-      <c r="C143">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3">
-      <c r="A144">
-        <v>21808</v>
-      </c>
-      <c r="B144">
-        <v>1</v>
-      </c>
-      <c r="C144">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3">
-      <c r="A145">
-        <v>22317</v>
-      </c>
-      <c r="B145">
-        <v>3</v>
-      </c>
-      <c r="C145">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3">
-      <c r="A146">
-        <v>22330</v>
-      </c>
-      <c r="B146">
-        <v>3</v>
-      </c>
-      <c r="C146">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3">
-      <c r="A147">
-        <v>22363</v>
-      </c>
-      <c r="B147">
-        <v>1</v>
-      </c>
-      <c r="C147">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3">
-      <c r="A148">
-        <v>23262</v>
-      </c>
-      <c r="B148">
-        <v>2</v>
-      </c>
-      <c r="C148">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3">
-      <c r="A149">
-        <v>23611</v>
-      </c>
-      <c r="B149">
-        <v>3</v>
-      </c>
-      <c r="C149">
         <v>8</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3">
-      <c r="A150">
-        <v>23992</v>
-      </c>
-      <c r="B150">
-        <v>29</v>
-      </c>
-      <c r="C150">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3">
-      <c r="A151">
-        <v>23994</v>
-      </c>
-      <c r="B151">
-        <v>29</v>
-      </c>
-      <c r="C151">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3">
-      <c r="A152">
-        <v>24256</v>
-      </c>
-      <c r="B152">
-        <v>1</v>
-      </c>
-      <c r="C152">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3">
-      <c r="A153">
-        <v>24257</v>
-      </c>
-      <c r="B153">
-        <v>1</v>
-      </c>
-      <c r="C153">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3">
-      <c r="A154">
-        <v>24258</v>
-      </c>
-      <c r="B154">
-        <v>1</v>
-      </c>
-      <c r="C154">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3">
-      <c r="A155">
-        <v>24260</v>
-      </c>
-      <c r="B155">
-        <v>1</v>
-      </c>
-      <c r="C155">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3">
-      <c r="A156">
-        <v>24707</v>
-      </c>
-      <c r="B156">
-        <v>3</v>
-      </c>
-      <c r="C156">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3">
-      <c r="A157">
-        <v>24712</v>
-      </c>
-      <c r="B157">
-        <v>3</v>
-      </c>
-      <c r="C157">
-        <v>702</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_700.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_700.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C150"/>
+  <dimension ref="A1:C146"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,318 +396,318 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>27</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3">
-        <v>126</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>196</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>37</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>137</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>159</v>
+        <v>71</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C7">
-        <v>406</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>168</v>
+        <v>83</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>227</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>374</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>220</v>
+        <v>94</v>
       </c>
       <c r="B10">
         <v>4</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>308</v>
+        <v>95</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>96</v>
+        <v>635</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>335</v>
+        <v>130</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>735</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>336</v>
+        <v>146</v>
       </c>
       <c r="B13">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>62</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>344</v>
+        <v>151</v>
       </c>
       <c r="B14">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>91</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>434</v>
+        <v>159</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15">
-        <v>56</v>
+        <v>417</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>435</v>
+        <v>161</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16">
-        <v>57</v>
+        <v>417</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>515</v>
+        <v>170</v>
       </c>
       <c r="B17">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>641</v>
+        <v>201</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>363</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>944</v>
+        <v>202</v>
       </c>
       <c r="B19">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>949</v>
+        <v>214</v>
       </c>
       <c r="B20">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C20">
-        <v>39</v>
+        <v>378</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>1055</v>
+        <v>216</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C21">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>1056</v>
+        <v>336</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C22">
-        <v>7</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>1059</v>
+        <v>344</v>
       </c>
       <c r="B23">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C23">
-        <v>192</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>1120</v>
+        <v>345</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C24">
-        <v>64</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>1134</v>
+        <v>424</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C25">
-        <v>25</v>
+        <v>309</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>1309</v>
+        <v>435</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26">
-        <v>31</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>1447</v>
+        <v>436</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27">
-        <v>8</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>1448</v>
+        <v>590</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C28">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>1622</v>
+        <v>616</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29">
-        <v>117</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>1656</v>
+        <v>641</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30">
         <v>7</v>
@@ -715,351 +715,351 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>1801</v>
+        <v>823</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
       <c r="C31">
-        <v>54</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>2103</v>
+        <v>903</v>
       </c>
       <c r="B32">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C32">
-        <v>195</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>2104</v>
+        <v>947</v>
       </c>
       <c r="B33">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C33">
-        <v>193</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>2109</v>
+        <v>949</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C34">
-        <v>22</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>2160</v>
+        <v>991</v>
       </c>
       <c r="B35">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C35">
-        <v>76</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>2422</v>
+        <v>1055</v>
       </c>
       <c r="B36">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C36">
-        <v>210</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>2424</v>
+        <v>1059</v>
       </c>
       <c r="B37">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C37">
-        <v>130</v>
+        <v>146</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>2497</v>
+        <v>1163</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38">
-        <v>95</v>
+        <v>196</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>2736</v>
+        <v>1446</v>
       </c>
       <c r="B39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C39">
-        <v>29</v>
+        <v>143</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2774</v>
+        <v>1447</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40">
-        <v>96</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2775</v>
+        <v>1601</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>164</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2991</v>
+        <v>1604</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C42">
-        <v>160</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>3016</v>
+        <v>1622</v>
       </c>
       <c r="B43">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C43">
-        <v>29</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>3021</v>
+        <v>1777</v>
       </c>
       <c r="B44">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C44">
-        <v>42</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>3049</v>
+        <v>1801</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>3430</v>
+        <v>2109</v>
       </c>
       <c r="B46">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>40</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>3434</v>
+        <v>2160</v>
       </c>
       <c r="B47">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C47">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>3454</v>
+        <v>2331</v>
       </c>
       <c r="B48">
         <v>1</v>
       </c>
       <c r="C48">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>3673</v>
+        <v>2423</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C49">
-        <v>138</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>3674</v>
+        <v>2726</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C50">
-        <v>135</v>
+        <v>72</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>3898</v>
+        <v>2878</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C51">
-        <v>21</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>3899</v>
+        <v>2879</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C52">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>4222</v>
+        <v>2935</v>
       </c>
       <c r="B53">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C53">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>4225</v>
+        <v>3434</v>
       </c>
       <c r="B54">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>4715</v>
+        <v>3454</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C55">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>4880</v>
+        <v>3673</v>
       </c>
       <c r="B56">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C56">
-        <v>14</v>
+        <v>142</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>4883</v>
+        <v>3893</v>
       </c>
       <c r="B57">
-        <v>332</v>
+        <v>1</v>
       </c>
       <c r="C57">
-        <v>7</v>
+        <v>86</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>4957</v>
+        <v>3899</v>
       </c>
       <c r="B58">
-        <v>332</v>
+        <v>3</v>
       </c>
       <c r="C58">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>4960</v>
+        <v>3900</v>
       </c>
       <c r="B59">
-        <v>332</v>
+        <v>3</v>
       </c>
       <c r="C59">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>4961</v>
+        <v>4019</v>
       </c>
       <c r="B60">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C60">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>4963</v>
+        <v>4178</v>
       </c>
       <c r="B61">
-        <v>332</v>
+        <v>68</v>
       </c>
       <c r="C61">
-        <v>41</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>4964</v>
+        <v>4225</v>
       </c>
       <c r="B62">
-        <v>332</v>
+        <v>4</v>
       </c>
       <c r="C62">
         <v>7</v>
@@ -1067,370 +1067,370 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>5152</v>
+        <v>4883</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>332</v>
       </c>
       <c r="C63">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>5153</v>
+        <v>4955</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>332</v>
       </c>
       <c r="C64">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5243</v>
+        <v>4957</v>
       </c>
       <c r="B65">
-        <v>3</v>
+        <v>332</v>
       </c>
       <c r="C65">
-        <v>148</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5341</v>
+        <v>5005</v>
       </c>
       <c r="B66">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C66">
-        <v>7</v>
+        <v>144</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5490</v>
+        <v>5083</v>
       </c>
       <c r="B67">
         <v>2</v>
       </c>
       <c r="C67">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5491</v>
+        <v>5152</v>
       </c>
       <c r="B68">
         <v>2</v>
       </c>
       <c r="C68">
-        <v>57</v>
+        <v>14</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5493</v>
+        <v>5153</v>
       </c>
       <c r="B69">
         <v>2</v>
       </c>
       <c r="C69">
-        <v>74</v>
+        <v>14</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5494</v>
+        <v>5208</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C70">
-        <v>57</v>
+        <v>321</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5584</v>
+        <v>5243</v>
       </c>
       <c r="B71">
         <v>3</v>
       </c>
       <c r="C71">
-        <v>264</v>
+        <v>150</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5647</v>
+        <v>5490</v>
       </c>
       <c r="B72">
         <v>2</v>
       </c>
       <c r="C72">
-        <v>7</v>
+        <v>56</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5653</v>
+        <v>5491</v>
       </c>
       <c r="B73">
         <v>2</v>
       </c>
       <c r="C73">
-        <v>7</v>
+        <v>57</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5723</v>
+        <v>5493</v>
       </c>
       <c r="B74">
         <v>2</v>
       </c>
       <c r="C74">
-        <v>34</v>
+        <v>57</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>5831</v>
+        <v>5494</v>
       </c>
       <c r="B75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C75">
-        <v>20</v>
+        <v>57</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>5966</v>
+        <v>5513</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76">
-        <v>8</v>
+        <v>46</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>5967</v>
+        <v>5723</v>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C77">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>6034</v>
+        <v>5733</v>
       </c>
       <c r="B78">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C78">
-        <v>380</v>
+        <v>37</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>6494</v>
+        <v>5966</v>
       </c>
       <c r="B79">
         <v>1</v>
       </c>
       <c r="C79">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>6497</v>
+        <v>5967</v>
       </c>
       <c r="B80">
         <v>1</v>
       </c>
       <c r="C80">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>6575</v>
+        <v>6034</v>
       </c>
       <c r="B81">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C81">
-        <v>193</v>
+        <v>739</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>6629</v>
+        <v>6494</v>
       </c>
       <c r="B82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C82">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>6927</v>
+        <v>6929</v>
       </c>
       <c r="B83">
         <v>12</v>
       </c>
       <c r="C83">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>6928</v>
+        <v>7318</v>
       </c>
       <c r="B84">
         <v>12</v>
       </c>
       <c r="C84">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>6929</v>
+        <v>7520</v>
       </c>
       <c r="B85">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>7007</v>
+        <v>8106</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C86">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>7318</v>
+        <v>8217</v>
       </c>
       <c r="B87">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C87">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>7520</v>
+        <v>8284</v>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88">
-        <v>7</v>
+        <v>274</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>8104</v>
+        <v>8939</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89">
-        <v>7</v>
+        <v>89</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>8106</v>
+        <v>8945</v>
       </c>
       <c r="B90">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C90">
-        <v>40</v>
+        <v>337</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>8217</v>
+        <v>9135</v>
       </c>
       <c r="B91">
-        <v>25</v>
+        <v>332</v>
       </c>
       <c r="C91">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>8284</v>
+        <v>9208</v>
       </c>
       <c r="B92">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C92">
-        <v>276</v>
+        <v>56</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>8915</v>
+        <v>9209</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C93">
-        <v>10</v>
+        <v>56</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>8926</v>
+        <v>9239</v>
       </c>
       <c r="B94">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C94">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>9081</v>
+        <v>9358</v>
       </c>
       <c r="B95">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C95">
-        <v>363</v>
+        <v>32</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>9135</v>
+        <v>9577</v>
       </c>
       <c r="B96">
         <v>332</v>
@@ -1441,54 +1441,54 @@
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>9577</v>
+        <v>9690</v>
       </c>
       <c r="B97">
-        <v>332</v>
+        <v>1</v>
       </c>
       <c r="C97">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>9789</v>
+        <v>9760</v>
       </c>
       <c r="B98">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C98">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>9830</v>
+        <v>9785</v>
       </c>
       <c r="B99">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C99">
-        <v>42</v>
+        <v>87</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>9833</v>
+        <v>9787</v>
       </c>
       <c r="B100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C100">
-        <v>70</v>
+        <v>41</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>10105</v>
+        <v>9789</v>
       </c>
       <c r="B101">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C101">
         <v>7</v>
@@ -1496,65 +1496,65 @@
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>10491</v>
+        <v>9829</v>
       </c>
       <c r="B102">
-        <v>332</v>
+        <v>3</v>
       </c>
       <c r="C102">
-        <v>7</v>
+        <v>53</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>10716</v>
+        <v>9833</v>
       </c>
       <c r="B103">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C103">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>10825</v>
+        <v>10105</v>
       </c>
       <c r="B104">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C104">
-        <v>385</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>11044</v>
+        <v>10716</v>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C105">
-        <v>26</v>
+        <v>59</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11046</v>
+        <v>10780</v>
       </c>
       <c r="B106">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C106">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11090</v>
+        <v>11114</v>
       </c>
       <c r="B107">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C107">
         <v>7</v>
@@ -1562,65 +1562,65 @@
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11114</v>
+        <v>11131</v>
       </c>
       <c r="B108">
         <v>23</v>
       </c>
       <c r="C108">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11116</v>
+        <v>11134</v>
       </c>
       <c r="B109">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C109">
-        <v>45</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11131</v>
+        <v>11150</v>
       </c>
       <c r="B110">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C110">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11134</v>
+        <v>11357</v>
       </c>
       <c r="B111">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C111">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11215</v>
+        <v>11467</v>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11357</v>
+        <v>11493</v>
       </c>
       <c r="B113">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C113">
         <v>7</v>
@@ -1628,54 +1628,54 @@
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11467</v>
+        <v>11555</v>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C114">
-        <v>121</v>
+        <v>74</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11493</v>
+        <v>11684</v>
       </c>
       <c r="B115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C115">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11555</v>
+        <v>11868</v>
       </c>
       <c r="B116">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C116">
-        <v>74</v>
+        <v>155</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>11583</v>
+        <v>11895</v>
       </c>
       <c r="B117">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C117">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>11684</v>
+        <v>12128</v>
       </c>
       <c r="B118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C118">
         <v>7</v>
@@ -1683,98 +1683,98 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>11855</v>
+        <v>12269</v>
       </c>
       <c r="B119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C119">
-        <v>58</v>
+        <v>37</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>11895</v>
+        <v>12536</v>
       </c>
       <c r="B120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C120">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>11914</v>
+        <v>12539</v>
       </c>
       <c r="B121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C121">
-        <v>44</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>11952</v>
+        <v>12764</v>
       </c>
       <c r="B122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C122">
-        <v>7</v>
+        <v>411</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12128</v>
+        <v>12925</v>
       </c>
       <c r="B123">
         <v>1</v>
       </c>
       <c r="C123">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12536</v>
+        <v>13259</v>
       </c>
       <c r="B124">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C124">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12539</v>
+        <v>13263</v>
       </c>
       <c r="B125">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C125">
-        <v>7</v>
+        <v>52</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12546</v>
+        <v>13264</v>
       </c>
       <c r="B126">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C126">
-        <v>7</v>
+        <v>78</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>12611</v>
+        <v>13266</v>
       </c>
       <c r="B127">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C127">
         <v>7</v>
@@ -1782,95 +1782,95 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>12923</v>
+        <v>13269</v>
       </c>
       <c r="B128">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C128">
-        <v>21</v>
+        <v>44</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>12924</v>
+        <v>13272</v>
       </c>
       <c r="B129">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C129">
-        <v>29</v>
+        <v>59</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>12925</v>
+        <v>13293</v>
       </c>
       <c r="B130">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C130">
-        <v>35</v>
+        <v>160</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>13023</v>
+        <v>13467</v>
       </c>
       <c r="B131">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C131">
-        <v>661</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>13028</v>
+        <v>14017</v>
       </c>
       <c r="B132">
         <v>3</v>
       </c>
       <c r="C132">
-        <v>82</v>
+        <v>115</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>13259</v>
+        <v>18964</v>
       </c>
       <c r="B133">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C133">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>13264</v>
+        <v>19924</v>
       </c>
       <c r="B134">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C134">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>13467</v>
+        <v>19980</v>
       </c>
       <c r="B135">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C135">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>14018</v>
+        <v>20208</v>
       </c>
       <c r="B136">
         <v>3</v>
@@ -1881,40 +1881,40 @@
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>18964</v>
+        <v>20486</v>
       </c>
       <c r="B137">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C137">
-        <v>7</v>
+        <v>346</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>20208</v>
+        <v>21082</v>
       </c>
       <c r="B138">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C138">
-        <v>7</v>
+        <v>210</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>21082</v>
+        <v>22049</v>
       </c>
       <c r="B139">
         <v>10</v>
       </c>
       <c r="C139">
-        <v>210</v>
+        <v>10</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>22049</v>
+        <v>22089</v>
       </c>
       <c r="B140">
         <v>10</v>
@@ -1925,112 +1925,68 @@
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>22089</v>
+        <v>22317</v>
       </c>
       <c r="B141">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C141">
-        <v>10</v>
+        <v>177</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>23491</v>
+        <v>23992</v>
       </c>
       <c r="B142">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C142">
-        <v>123</v>
+        <v>31</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>23992</v>
+        <v>24252</v>
       </c>
       <c r="B143">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C143">
-        <v>31</v>
+        <v>107</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>24125</v>
+        <v>24257</v>
       </c>
       <c r="B144">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C144">
-        <v>7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>24252</v>
+        <v>24258</v>
       </c>
       <c r="B145">
         <v>1</v>
       </c>
       <c r="C145">
-        <v>105</v>
+        <v>78</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>24257</v>
+        <v>25958</v>
       </c>
       <c r="B146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C146">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3">
-      <c r="A147">
-        <v>24260</v>
-      </c>
-      <c r="B147">
-        <v>1</v>
-      </c>
-      <c r="C147">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3">
-      <c r="A148">
-        <v>24707</v>
-      </c>
-      <c r="B148">
-        <v>3</v>
-      </c>
-      <c r="C148">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3">
-      <c r="A149">
-        <v>25278</v>
-      </c>
-      <c r="B149">
-        <v>2</v>
-      </c>
-      <c r="C149">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3">
-      <c r="A150">
-        <v>25899</v>
-      </c>
-      <c r="B150">
-        <v>2</v>
-      </c>
-      <c r="C150">
-        <v>95</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_700.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_700.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C150"/>
+  <dimension ref="A1:C149"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,266 +396,266 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3">
-        <v>63</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>83</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5">
-        <v>84</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6">
-        <v>121</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8">
-        <v>28</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>38</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>641</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>151</v>
+        <v>80</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12">
-        <v>73</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="B13">
         <v>3</v>
       </c>
       <c r="C13">
-        <v>10</v>
+        <v>641</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>168</v>
+        <v>107</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>218</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>201</v>
+        <v>126</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>182</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>211</v>
+        <v>144</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16">
-        <v>37</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>215</v>
+        <v>159</v>
       </c>
       <c r="B17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>401</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>216</v>
+        <v>167</v>
       </c>
       <c r="B18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18">
-        <v>23</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>308</v>
+        <v>211</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>94</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>336</v>
+        <v>214</v>
       </c>
       <c r="B20">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C20">
-        <v>123</v>
+        <v>374</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>344</v>
+        <v>215</v>
       </c>
       <c r="B21">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C21">
-        <v>91</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="B22">
         <v>3</v>
       </c>
       <c r="C22">
-        <v>182</v>
+        <v>719</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>436</v>
+        <v>411</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23">
-        <v>111</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>515</v>
+        <v>436</v>
       </c>
       <c r="B24">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>590</v>
+        <v>615</v>
       </c>
       <c r="B25">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C25">
-        <v>54</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -666,7 +666,7 @@
         <v>2</v>
       </c>
       <c r="C26">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -682,13 +682,13 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="B28">
         <v>15</v>
       </c>
       <c r="C28">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -715,244 +715,244 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="B31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C31">
-        <v>56</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>952</v>
+        <v>957</v>
       </c>
       <c r="B32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C32">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>955</v>
+        <v>974</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C33">
-        <v>7</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>957</v>
+        <v>991</v>
       </c>
       <c r="B34">
         <v>2</v>
       </c>
       <c r="C34">
-        <v>57</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>991</v>
+        <v>1055</v>
       </c>
       <c r="B35">
         <v>2</v>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1055</v>
+        <v>1070</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C36">
-        <v>21</v>
+        <v>415</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1056</v>
+        <v>1120</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1059</v>
+        <v>1134</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>142</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>1406</v>
+        <v>1447</v>
       </c>
       <c r="B39">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C39">
-        <v>46</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>1409</v>
+        <v>1492</v>
       </c>
       <c r="B40">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C40">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>1446</v>
+        <v>1601</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C41">
-        <v>73</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>1447</v>
+        <v>1801</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42">
-        <v>8</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>1448</v>
+        <v>2108</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C43">
-        <v>7</v>
+        <v>287</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>1601</v>
+        <v>2160</v>
       </c>
       <c r="B44">
         <v>68</v>
       </c>
       <c r="C44">
-        <v>164</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>1604</v>
+        <v>2331</v>
       </c>
       <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
         <v>68</v>
-      </c>
-      <c r="C45">
-        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>1622</v>
+        <v>2423</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C46">
-        <v>57</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>1801</v>
+        <v>2438</v>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47">
-        <v>57</v>
+        <v>719</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2109</v>
+        <v>2537</v>
       </c>
       <c r="B48">
         <v>1</v>
       </c>
       <c r="C48">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2160</v>
+        <v>2538</v>
       </c>
       <c r="B49">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C49">
-        <v>76</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2322</v>
+        <v>2539</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C50">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2331</v>
+        <v>2729</v>
       </c>
       <c r="B51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C51">
-        <v>184</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2335</v>
+        <v>2774</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C52">
-        <v>7</v>
+        <v>98</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -963,51 +963,51 @@
         <v>1</v>
       </c>
       <c r="C53">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>2916</v>
+        <v>2912</v>
       </c>
       <c r="B54">
         <v>1</v>
       </c>
       <c r="C54">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>2934</v>
+        <v>2991</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C55">
-        <v>16</v>
+        <v>159</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>2935</v>
+        <v>3016</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C56">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>2991</v>
+        <v>3257</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C57">
-        <v>160</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1018,7 +1018,7 @@
         <v>2</v>
       </c>
       <c r="C58">
-        <v>101</v>
+        <v>51</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1029,111 +1029,111 @@
         <v>1</v>
       </c>
       <c r="C59">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3673</v>
+        <v>3495</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C60">
-        <v>144</v>
+        <v>564</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>4178</v>
+        <v>3673</v>
       </c>
       <c r="B61">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C61">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>4223</v>
+        <v>3898</v>
       </c>
       <c r="B62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C62">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>4225</v>
+        <v>3982</v>
       </c>
       <c r="B63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C63">
-        <v>7</v>
+        <v>464</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>4715</v>
+        <v>4019</v>
       </c>
       <c r="B64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C64">
-        <v>23</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>4718</v>
+        <v>4223</v>
       </c>
       <c r="B65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C65">
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>4880</v>
+        <v>4225</v>
       </c>
       <c r="B66">
-        <v>332</v>
+        <v>4</v>
       </c>
       <c r="C66">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>4883</v>
+        <v>4246</v>
       </c>
       <c r="B67">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>4955</v>
+        <v>4883</v>
       </c>
       <c r="B68">
         <v>332</v>
       </c>
       <c r="C68">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>4957</v>
+        <v>4955</v>
       </c>
       <c r="B69">
         <v>332</v>
@@ -1144,57 +1144,57 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>4960</v>
+        <v>4957</v>
       </c>
       <c r="B70">
         <v>332</v>
       </c>
       <c r="C70">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>4961</v>
+        <v>5083</v>
       </c>
       <c r="B71">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C71">
-        <v>24</v>
+        <v>70</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5083</v>
+        <v>5152</v>
       </c>
       <c r="B72">
         <v>2</v>
       </c>
       <c r="C72">
-        <v>71</v>
+        <v>14</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5152</v>
+        <v>5153</v>
       </c>
       <c r="B73">
         <v>2</v>
       </c>
       <c r="C73">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5153</v>
+        <v>5165</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C74">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1210,13 +1210,13 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>5341</v>
+        <v>5434</v>
       </c>
       <c r="B76">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1227,7 +1227,7 @@
         <v>2</v>
       </c>
       <c r="C77">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1238,7 +1238,7 @@
         <v>2</v>
       </c>
       <c r="C78">
-        <v>57</v>
+        <v>110</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1249,29 +1249,29 @@
         <v>2</v>
       </c>
       <c r="C79">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>5584</v>
+        <v>5513</v>
       </c>
       <c r="B80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C80">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>5813</v>
+        <v>5653</v>
       </c>
       <c r="B81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C81">
-        <v>440</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1304,7 +1304,7 @@
         <v>23</v>
       </c>
       <c r="C84">
-        <v>731</v>
+        <v>717</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1320,29 +1320,29 @@
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>6098</v>
+        <v>6494</v>
       </c>
       <c r="B86">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>6494</v>
+        <v>6496</v>
       </c>
       <c r="B87">
         <v>1</v>
       </c>
       <c r="C87">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B88">
         <v>3</v>
@@ -1353,54 +1353,54 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>6929</v>
+        <v>6927</v>
       </c>
       <c r="B89">
         <v>12</v>
       </c>
       <c r="C89">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>7520</v>
+        <v>6929</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C90">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>8106</v>
+        <v>7318</v>
       </c>
       <c r="B91">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C91">
-        <v>40</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>8217</v>
+        <v>7520</v>
       </c>
       <c r="B92">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C92">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>8557</v>
+        <v>8104</v>
       </c>
       <c r="B93">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C93">
         <v>7</v>
@@ -1408,98 +1408,98 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>8945</v>
+        <v>8217</v>
       </c>
       <c r="B94">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C94">
-        <v>332</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>9081</v>
+        <v>8853</v>
       </c>
       <c r="B95">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C95">
-        <v>363</v>
+        <v>308</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>9208</v>
+        <v>8898</v>
       </c>
       <c r="B96">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C96">
-        <v>56</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>9577</v>
+        <v>8926</v>
       </c>
       <c r="B97">
-        <v>332</v>
+        <v>1</v>
       </c>
       <c r="C97">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>9613</v>
+        <v>9081</v>
       </c>
       <c r="B98">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C98">
-        <v>46</v>
+        <v>542</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>9691</v>
+        <v>9208</v>
       </c>
       <c r="B99">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C99">
-        <v>82</v>
+        <v>57</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>9760</v>
+        <v>9577</v>
       </c>
       <c r="B100">
-        <v>29</v>
+        <v>332</v>
       </c>
       <c r="C100">
-        <v>147</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>9789</v>
+        <v>9613</v>
       </c>
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>10105</v>
+        <v>9789</v>
       </c>
       <c r="B102">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C102">
         <v>7</v>
@@ -1507,87 +1507,87 @@
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>10149</v>
+        <v>9828</v>
       </c>
       <c r="B103">
         <v>3</v>
       </c>
       <c r="C103">
-        <v>534</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>10491</v>
+        <v>9833</v>
       </c>
       <c r="B104">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C104">
-        <v>7</v>
+        <v>71</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>10530</v>
+        <v>10105</v>
       </c>
       <c r="B105">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C105">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>10780</v>
+        <v>10530</v>
       </c>
       <c r="B106">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C106">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11044</v>
+        <v>10825</v>
       </c>
       <c r="B107">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C107">
-        <v>27</v>
+        <v>739</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11046</v>
+        <v>11090</v>
       </c>
       <c r="B108">
         <v>1</v>
       </c>
       <c r="C108">
-        <v>27</v>
+        <v>46</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11090</v>
+        <v>11114</v>
       </c>
       <c r="B109">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C109">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11092</v>
+        <v>11131</v>
       </c>
       <c r="B110">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C110">
         <v>7</v>
@@ -1595,123 +1595,123 @@
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11114</v>
+        <v>11134</v>
       </c>
       <c r="B111">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C111">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11131</v>
+        <v>11150</v>
       </c>
       <c r="B112">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C112">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11134</v>
+        <v>11357</v>
       </c>
       <c r="B113">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C113">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11150</v>
+        <v>11403</v>
       </c>
       <c r="B114">
         <v>1</v>
       </c>
       <c r="C114">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11357</v>
+        <v>11492</v>
       </c>
       <c r="B115">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C115">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11467</v>
+        <v>11493</v>
       </c>
       <c r="B116">
         <v>1</v>
       </c>
       <c r="C116">
-        <v>59</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>11492</v>
+        <v>11555</v>
       </c>
       <c r="B117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C117">
-        <v>50</v>
+        <v>74</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>11493</v>
+        <v>11583</v>
       </c>
       <c r="B118">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C118">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>11495</v>
+        <v>11855</v>
       </c>
       <c r="B119">
         <v>1</v>
       </c>
       <c r="C119">
-        <v>27</v>
+        <v>58</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>11644</v>
+        <v>11895</v>
       </c>
       <c r="B120">
         <v>1</v>
       </c>
       <c r="C120">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>11895</v>
+        <v>11914</v>
       </c>
       <c r="B121">
         <v>1</v>
       </c>
       <c r="C121">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -1749,101 +1749,101 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12059</v>
+        <v>12128</v>
       </c>
       <c r="B125">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C125">
-        <v>162</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12128</v>
+        <v>12536</v>
       </c>
       <c r="B126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C126">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>12536</v>
+        <v>12539</v>
       </c>
       <c r="B127">
         <v>2</v>
       </c>
       <c r="C127">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>12539</v>
+        <v>12924</v>
       </c>
       <c r="B128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C128">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>12611</v>
+        <v>12925</v>
       </c>
       <c r="B129">
         <v>1</v>
       </c>
       <c r="C129">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>12764</v>
+        <v>13249</v>
       </c>
       <c r="B130">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C130">
-        <v>411</v>
+        <v>72</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>12925</v>
+        <v>13260</v>
       </c>
       <c r="B131">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C131">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>13249</v>
+        <v>13264</v>
       </c>
       <c r="B132">
         <v>29</v>
       </c>
       <c r="C132">
-        <v>71</v>
+        <v>40</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>13260</v>
+        <v>13266</v>
       </c>
       <c r="B133">
         <v>29</v>
       </c>
       <c r="C133">
-        <v>40</v>
+        <v>64</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -1854,7 +1854,7 @@
         <v>29</v>
       </c>
       <c r="C134">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -1865,7 +1865,7 @@
         <v>29</v>
       </c>
       <c r="C135">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -1881,7 +1881,7 @@
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>14018</v>
+        <v>14017</v>
       </c>
       <c r="B137">
         <v>3</v>
@@ -1892,145 +1892,134 @@
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>19924</v>
+        <v>18964</v>
       </c>
       <c r="B138">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C138">
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>19980</v>
+        <v>19924</v>
       </c>
       <c r="B139">
         <v>2</v>
       </c>
       <c r="C139">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>19987</v>
+        <v>21082</v>
       </c>
       <c r="B140">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C140">
-        <v>36</v>
+        <v>216</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>20208</v>
+        <v>22049</v>
       </c>
       <c r="B141">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C141">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>21082</v>
+        <v>22089</v>
       </c>
       <c r="B142">
         <v>10</v>
       </c>
       <c r="C142">
-        <v>213</v>
+        <v>118</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>21269</v>
+        <v>22317</v>
       </c>
       <c r="B143">
         <v>3</v>
       </c>
       <c r="C143">
-        <v>523</v>
+        <v>179</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>21798</v>
+        <v>23238</v>
       </c>
       <c r="B144">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C144">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>21946</v>
+        <v>23992</v>
       </c>
       <c r="B145">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C145">
-        <v>7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>22049</v>
+        <v>24252</v>
       </c>
       <c r="B146">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C146">
-        <v>10</v>
+        <v>109</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>22089</v>
+        <v>24257</v>
       </c>
       <c r="B147">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C147">
-        <v>10</v>
+        <v>79</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>23992</v>
+        <v>24260</v>
       </c>
       <c r="B148">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C148">
-        <v>31</v>
+        <v>79</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>24252</v>
+        <v>25278</v>
       </c>
       <c r="B149">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C149">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3">
-      <c r="A150">
-        <v>24257</v>
-      </c>
-      <c r="B150">
-        <v>1</v>
-      </c>
-      <c r="C150">
-        <v>82</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_700.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_700.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C149"/>
+  <dimension ref="A1:C150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -402,631 +402,631 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3">
-        <v>27</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>64</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5">
-        <v>125</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6">
-        <v>63</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8">
-        <v>64</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9">
-        <v>62</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>62</v>
+        <v>641</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>48</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C12">
-        <v>28</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>95</v>
+        <v>143</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>641</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14">
-        <v>26</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>144</v>
+        <v>214</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16">
-        <v>86</v>
+        <v>711</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17">
-        <v>401</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>167</v>
+        <v>305</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>126</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>211</v>
+        <v>308</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>214</v>
+        <v>335</v>
       </c>
       <c r="B20">
         <v>3</v>
       </c>
       <c r="C20">
-        <v>374</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>215</v>
+        <v>414</v>
       </c>
       <c r="B21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>21</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>335</v>
+        <v>436</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>719</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>411</v>
+        <v>470</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>59</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>436</v>
+        <v>615</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24">
-        <v>56</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25">
-        <v>13</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>616</v>
+        <v>641</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>57</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>641</v>
+        <v>949</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>944</v>
+        <v>957</v>
       </c>
       <c r="B28">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>25</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>949</v>
+        <v>991</v>
       </c>
       <c r="B29">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C29">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>950</v>
+        <v>1055</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>955</v>
+        <v>1070</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C31">
-        <v>116</v>
+        <v>406</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>957</v>
+        <v>1134</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32">
-        <v>58</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>974</v>
+        <v>1447</v>
       </c>
       <c r="B33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C33">
-        <v>110</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>991</v>
+        <v>1492</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1055</v>
+        <v>1601</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C35">
-        <v>21</v>
+        <v>164</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1070</v>
+        <v>1604</v>
       </c>
       <c r="B36">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="C36">
-        <v>415</v>
+        <v>264</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1120</v>
+        <v>2108</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C37">
-        <v>64</v>
+        <v>284</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1134</v>
+        <v>2331</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
       <c r="C38">
-        <v>24</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>1447</v>
+        <v>2423</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C39">
-        <v>8</v>
+        <v>202</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>1492</v>
+        <v>2438</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>21</v>
+        <v>352</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>1601</v>
+        <v>2537</v>
       </c>
       <c r="B41">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>1801</v>
+        <v>2538</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42">
-        <v>54</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2108</v>
+        <v>2729</v>
       </c>
       <c r="B43">
         <v>3</v>
       </c>
       <c r="C43">
-        <v>287</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2160</v>
+        <v>2774</v>
       </c>
       <c r="B44">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>76</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2331</v>
+        <v>2912</v>
       </c>
       <c r="B45">
         <v>1</v>
       </c>
       <c r="C45">
-        <v>68</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2423</v>
+        <v>2991</v>
       </c>
       <c r="B46">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C46">
-        <v>105</v>
+        <v>159</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2438</v>
+        <v>3016</v>
       </c>
       <c r="B47">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C47">
-        <v>719</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2537</v>
+        <v>3258</v>
       </c>
       <c r="B48">
         <v>1</v>
       </c>
       <c r="C48">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2538</v>
+        <v>3434</v>
       </c>
       <c r="B49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49">
-        <v>17</v>
+        <v>67</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2539</v>
+        <v>3454</v>
       </c>
       <c r="B50">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2729</v>
+        <v>3462</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C51">
-        <v>49</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2774</v>
+        <v>3475</v>
       </c>
       <c r="B52">
         <v>2</v>
       </c>
       <c r="C52">
-        <v>98</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>2879</v>
+        <v>3495</v>
       </c>
       <c r="B53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C53">
-        <v>42</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>2912</v>
+        <v>3576</v>
       </c>
       <c r="B54">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C54">
-        <v>27</v>
+        <v>58</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>2991</v>
+        <v>3577</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C55">
-        <v>159</v>
+        <v>96</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3016</v>
+        <v>3899</v>
       </c>
       <c r="B56">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="C56">
-        <v>35</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3257</v>
+        <v>3982</v>
       </c>
       <c r="B57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C57">
-        <v>7</v>
+        <v>464</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3434</v>
+        <v>4223</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C58">
-        <v>51</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3454</v>
+        <v>4225</v>
       </c>
       <c r="B59">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C59">
         <v>7</v>
@@ -1034,175 +1034,175 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3495</v>
+        <v>4246</v>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C60">
-        <v>564</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>3673</v>
+        <v>4883</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>332</v>
       </c>
       <c r="C61">
-        <v>144</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3898</v>
+        <v>4955</v>
       </c>
       <c r="B62">
-        <v>3</v>
+        <v>332</v>
       </c>
       <c r="C62">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>3982</v>
+        <v>4957</v>
       </c>
       <c r="B63">
-        <v>3</v>
+        <v>332</v>
       </c>
       <c r="C63">
-        <v>464</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>4019</v>
+        <v>4960</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>332</v>
       </c>
       <c r="C64">
-        <v>51</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>4223</v>
+        <v>5083</v>
       </c>
       <c r="B65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C65">
-        <v>7</v>
+        <v>70</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>4225</v>
+        <v>5152</v>
       </c>
       <c r="B66">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C66">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>4246</v>
+        <v>5153</v>
       </c>
       <c r="B67">
         <v>2</v>
       </c>
       <c r="C67">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>4883</v>
+        <v>5165</v>
       </c>
       <c r="B68">
-        <v>332</v>
+        <v>1</v>
       </c>
       <c r="C68">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>4955</v>
+        <v>5243</v>
       </c>
       <c r="B69">
-        <v>332</v>
+        <v>3</v>
       </c>
       <c r="C69">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>4957</v>
+        <v>5434</v>
       </c>
       <c r="B70">
-        <v>332</v>
+        <v>1</v>
       </c>
       <c r="C70">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5083</v>
+        <v>5490</v>
       </c>
       <c r="B71">
         <v>2</v>
       </c>
       <c r="C71">
-        <v>70</v>
+        <v>57</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5152</v>
+        <v>5494</v>
       </c>
       <c r="B72">
         <v>2</v>
       </c>
       <c r="C72">
-        <v>14</v>
+        <v>57</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5153</v>
+        <v>5513</v>
       </c>
       <c r="B73">
         <v>2</v>
       </c>
       <c r="C73">
-        <v>13</v>
+        <v>44</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5165</v>
+        <v>5966</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>5243</v>
+        <v>5967</v>
       </c>
       <c r="B75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C75">
         <v>7</v>
@@ -1210,65 +1210,65 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>5434</v>
+        <v>6097</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C76">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>5490</v>
+        <v>6494</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>57</v>
+        <v>28</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>5491</v>
+        <v>6496</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78">
-        <v>110</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>5493</v>
+        <v>6497</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79">
-        <v>74</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>5513</v>
+        <v>6627</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C80">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>5653</v>
+        <v>6628</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C81">
         <v>7</v>
@@ -1276,21 +1276,21 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>5966</v>
+        <v>6927</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C82">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>5967</v>
+        <v>6929</v>
       </c>
       <c r="B83">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C83">
         <v>7</v>
@@ -1298,186 +1298,186 @@
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>6034</v>
+        <v>7318</v>
       </c>
       <c r="B84">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C84">
-        <v>717</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>6097</v>
+        <v>7520</v>
       </c>
       <c r="B85">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>77</v>
+        <v>12</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>6494</v>
+        <v>7703</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>6496</v>
+        <v>8104</v>
       </c>
       <c r="B87">
         <v>1</v>
       </c>
       <c r="C87">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>6627</v>
+        <v>8106</v>
       </c>
       <c r="B88">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C88">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>6927</v>
+        <v>8121</v>
       </c>
       <c r="B89">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C89">
-        <v>7</v>
+        <v>330</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>6929</v>
+        <v>8217</v>
       </c>
       <c r="B90">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C90">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>7318</v>
+        <v>8853</v>
       </c>
       <c r="B91">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C91">
-        <v>9</v>
+        <v>149</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>7520</v>
+        <v>8898</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C92">
-        <v>12</v>
+        <v>320</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>8104</v>
+        <v>8926</v>
       </c>
       <c r="B93">
         <v>1</v>
       </c>
       <c r="C93">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>8217</v>
+        <v>9135</v>
       </c>
       <c r="B94">
-        <v>25</v>
+        <v>332</v>
       </c>
       <c r="C94">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>8853</v>
+        <v>9208</v>
       </c>
       <c r="B95">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C95">
-        <v>308</v>
+        <v>55</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>8898</v>
+        <v>9289</v>
       </c>
       <c r="B96">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C96">
-        <v>7</v>
+        <v>71</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>8926</v>
+        <v>9577</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>332</v>
       </c>
       <c r="C97">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>9081</v>
+        <v>9778</v>
       </c>
       <c r="B98">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C98">
-        <v>542</v>
+        <v>26</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>9208</v>
+        <v>9786</v>
       </c>
       <c r="B99">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C99">
-        <v>57</v>
+        <v>40</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>9577</v>
+        <v>9789</v>
       </c>
       <c r="B100">
-        <v>332</v>
+        <v>1</v>
       </c>
       <c r="C100">
         <v>7</v>
@@ -1485,29 +1485,29 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>9613</v>
+        <v>9828</v>
       </c>
       <c r="B101">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C101">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>9789</v>
+        <v>9829</v>
       </c>
       <c r="B102">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C102">
-        <v>7</v>
+        <v>52</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>9828</v>
+        <v>10105</v>
       </c>
       <c r="B103">
         <v>3</v>
@@ -1518,134 +1518,134 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>9833</v>
+        <v>10491</v>
       </c>
       <c r="B104">
-        <v>2</v>
+        <v>332</v>
       </c>
       <c r="C104">
-        <v>71</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>10105</v>
+        <v>10716</v>
       </c>
       <c r="B105">
         <v>3</v>
       </c>
       <c r="C105">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>10530</v>
+        <v>10719</v>
       </c>
       <c r="B106">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="C106">
-        <v>28</v>
+        <v>56</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>10825</v>
+        <v>10720</v>
       </c>
       <c r="B107">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="C107">
-        <v>739</v>
+        <v>55</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11090</v>
+        <v>11039</v>
       </c>
       <c r="B108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C108">
-        <v>46</v>
+        <v>117</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11114</v>
+        <v>11044</v>
       </c>
       <c r="B109">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C109">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11131</v>
+        <v>11090</v>
       </c>
       <c r="B110">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C110">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11134</v>
+        <v>11114</v>
       </c>
       <c r="B111">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C111">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11150</v>
+        <v>11131</v>
       </c>
       <c r="B112">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C112">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11357</v>
+        <v>11134</v>
       </c>
       <c r="B113">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C113">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11403</v>
+        <v>11150</v>
       </c>
       <c r="B114">
         <v>1</v>
       </c>
       <c r="C114">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11492</v>
+        <v>11357</v>
       </c>
       <c r="B115">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C115">
-        <v>50</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -1661,13 +1661,13 @@
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>11555</v>
+        <v>11495</v>
       </c>
       <c r="B117">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C117">
-        <v>74</v>
+        <v>27</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -1711,48 +1711,48 @@
         <v>1</v>
       </c>
       <c r="C121">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>11961</v>
+        <v>11952</v>
       </c>
       <c r="B122">
         <v>1</v>
       </c>
       <c r="C122">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>11962</v>
+        <v>12128</v>
       </c>
       <c r="B123">
         <v>1</v>
       </c>
       <c r="C123">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>11965</v>
+        <v>12536</v>
       </c>
       <c r="B124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C124">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12128</v>
+        <v>12539</v>
       </c>
       <c r="B125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C125">
         <v>7</v>
@@ -1760,21 +1760,21 @@
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12536</v>
+        <v>12607</v>
       </c>
       <c r="B126">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C126">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>12539</v>
+        <v>12608</v>
       </c>
       <c r="B127">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C127">
         <v>7</v>
@@ -1782,117 +1782,117 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>12924</v>
+        <v>12675</v>
       </c>
       <c r="B128">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C128">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>12925</v>
+        <v>12676</v>
       </c>
       <c r="B129">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C129">
-        <v>36</v>
+        <v>62</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>13249</v>
+        <v>12677</v>
       </c>
       <c r="B130">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C130">
-        <v>72</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>13260</v>
+        <v>12924</v>
       </c>
       <c r="B131">
+        <v>1</v>
+      </c>
+      <c r="C131">
         <v>29</v>
-      </c>
-      <c r="C131">
-        <v>40</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>13264</v>
+        <v>12925</v>
       </c>
       <c r="B132">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C132">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>13266</v>
+        <v>13249</v>
       </c>
       <c r="B133">
         <v>29</v>
       </c>
       <c r="C133">
-        <v>64</v>
+        <v>14</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>13269</v>
+        <v>13264</v>
       </c>
       <c r="B134">
         <v>29</v>
       </c>
       <c r="C134">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>13272</v>
+        <v>13266</v>
       </c>
       <c r="B135">
         <v>29</v>
       </c>
       <c r="C135">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>13467</v>
+        <v>13269</v>
       </c>
       <c r="B136">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C136">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>14017</v>
+        <v>13272</v>
       </c>
       <c r="B137">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C137">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>18964</v>
+        <v>13467</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -1903,123 +1903,134 @@
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>19924</v>
+        <v>14017</v>
       </c>
       <c r="B139">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C139">
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>21082</v>
+        <v>14018</v>
       </c>
       <c r="B140">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C140">
-        <v>216</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>22049</v>
+        <v>19924</v>
       </c>
       <c r="B141">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C141">
-        <v>10</v>
+        <v>37</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>22089</v>
+        <v>21082</v>
       </c>
       <c r="B142">
         <v>10</v>
       </c>
       <c r="C142">
-        <v>118</v>
+        <v>219</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>22317</v>
+        <v>22049</v>
       </c>
       <c r="B143">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C143">
-        <v>179</v>
+        <v>10</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>23238</v>
+        <v>22089</v>
       </c>
       <c r="B144">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C144">
-        <v>40</v>
+        <v>120</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>23992</v>
+        <v>22317</v>
       </c>
       <c r="B145">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C145">
-        <v>31</v>
+        <v>165</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>24252</v>
+        <v>23234</v>
       </c>
       <c r="B146">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C146">
-        <v>109</v>
+        <v>53</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>24257</v>
+        <v>23238</v>
       </c>
       <c r="B147">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C147">
-        <v>79</v>
+        <v>40</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>24260</v>
+        <v>23992</v>
       </c>
       <c r="B148">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C148">
-        <v>79</v>
+        <v>31</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>25278</v>
+        <v>24252</v>
       </c>
       <c r="B149">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C149">
-        <v>158</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150">
+        <v>24260</v>
+      </c>
+      <c r="B150">
+        <v>1</v>
+      </c>
+      <c r="C150">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_700.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_700.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C150"/>
+  <dimension ref="A1:C148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -402,7 +402,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -413,642 +413,642 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>124</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5">
-        <v>62</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6">
-        <v>83</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>62</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>48</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>641</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C11">
-        <v>149</v>
+        <v>549</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12">
-        <v>149</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>143</v>
+        <v>95</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13">
-        <v>86</v>
+        <v>699</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14">
-        <v>86</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="B15">
         <v>3</v>
       </c>
       <c r="C15">
-        <v>10</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>214</v>
+        <v>141</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>711</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>215</v>
+        <v>143</v>
       </c>
       <c r="B17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C17">
-        <v>49</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>305</v>
+        <v>144</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>308</v>
+        <v>145</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>7</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>335</v>
+        <v>146</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20">
-        <v>18</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>414</v>
+        <v>159</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C21">
-        <v>94</v>
+        <v>425</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>436</v>
+        <v>168</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22">
-        <v>56</v>
+        <v>391</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>470</v>
+        <v>211</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>615</v>
+        <v>216</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C24">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>616</v>
+        <v>308</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>641</v>
+        <v>336</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C26">
-        <v>7</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>949</v>
+        <v>362</v>
       </c>
       <c r="B27">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C27">
-        <v>40</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>957</v>
+        <v>411</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
       <c r="C28">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>991</v>
+        <v>412</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>7</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>1055</v>
+        <v>413</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>21</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>1070</v>
+        <v>414</v>
       </c>
       <c r="B31">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C31">
-        <v>406</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1134</v>
+        <v>436</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32">
-        <v>25</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1447</v>
+        <v>515</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C33">
-        <v>8</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1492</v>
+        <v>590</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C34">
-        <v>20</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1601</v>
+        <v>949</v>
       </c>
       <c r="B35">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="C35">
-        <v>164</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1604</v>
+        <v>951</v>
       </c>
       <c r="B36">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="C36">
-        <v>264</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>2108</v>
+        <v>952</v>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C37">
-        <v>284</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>2331</v>
+        <v>972</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C38">
-        <v>70</v>
+        <v>353</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>2423</v>
+        <v>990</v>
       </c>
       <c r="B39">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C39">
-        <v>202</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2438</v>
+        <v>1070</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C40">
-        <v>352</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2537</v>
+        <v>1080</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C41">
-        <v>21</v>
+        <v>133</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2538</v>
+        <v>1082</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2729</v>
+        <v>1447</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C43">
-        <v>96</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2774</v>
+        <v>1492</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44">
-        <v>100</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2912</v>
+        <v>1598</v>
       </c>
       <c r="B45">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C45">
-        <v>27</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2991</v>
+        <v>1776</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>159</v>
+        <v>64</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>3016</v>
+        <v>1801</v>
       </c>
       <c r="B47">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C47">
-        <v>35</v>
+        <v>95</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>3258</v>
+        <v>2049</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C48">
-        <v>22</v>
+        <v>323</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>3434</v>
+        <v>2057</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C49">
-        <v>67</v>
+        <v>277</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>3454</v>
+        <v>2108</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C50">
-        <v>7</v>
+        <v>154</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>3462</v>
+        <v>2109</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51">
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>3475</v>
+        <v>2328</v>
       </c>
       <c r="B52">
         <v>2</v>
       </c>
       <c r="C52">
-        <v>7</v>
+        <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>3495</v>
+        <v>2331</v>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C53">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>3576</v>
+        <v>2422</v>
       </c>
       <c r="B54">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="C54">
-        <v>58</v>
+        <v>109</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3577</v>
+        <v>2726</v>
       </c>
       <c r="B55">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C55">
-        <v>96</v>
+        <v>76</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3899</v>
+        <v>2859</v>
       </c>
       <c r="B56">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C56">
-        <v>21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3982</v>
+        <v>2879</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C57">
-        <v>464</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>4223</v>
+        <v>2912</v>
       </c>
       <c r="B58">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C58">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>4225</v>
+        <v>2916</v>
       </c>
       <c r="B59">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C59">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>4246</v>
+        <v>2991</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C60">
-        <v>12</v>
+        <v>139</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>4883</v>
+        <v>3454</v>
       </c>
       <c r="B61">
-        <v>332</v>
+        <v>1</v>
       </c>
       <c r="C61">
         <v>7</v>
@@ -1056,112 +1056,112 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>4955</v>
+        <v>3577</v>
       </c>
       <c r="B62">
-        <v>332</v>
+        <v>25</v>
       </c>
       <c r="C62">
-        <v>15</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>4957</v>
+        <v>4246</v>
       </c>
       <c r="B63">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C63">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>4960</v>
+        <v>5151</v>
       </c>
       <c r="B64">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C64">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5083</v>
+        <v>5165</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5152</v>
+        <v>5208</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C66">
-        <v>14</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5153</v>
+        <v>5243</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C67">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5165</v>
+        <v>5435</v>
       </c>
       <c r="B68">
         <v>1</v>
       </c>
       <c r="C68">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5243</v>
+        <v>5490</v>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C69">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5434</v>
+        <v>5491</v>
       </c>
       <c r="B70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5490</v>
+        <v>5493</v>
       </c>
       <c r="B71">
         <v>2</v>
       </c>
       <c r="C71">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1172,7 +1172,7 @@
         <v>2</v>
       </c>
       <c r="C72">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1183,23 +1183,23 @@
         <v>2</v>
       </c>
       <c r="C73">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5966</v>
+        <v>5723</v>
       </c>
       <c r="B74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C74">
-        <v>8</v>
+        <v>37</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>5967</v>
+        <v>5966</v>
       </c>
       <c r="B75">
         <v>1</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>6097</v>
+        <v>5967</v>
       </c>
       <c r="B76">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C76">
         <v>7</v>
@@ -1221,35 +1221,35 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>6494</v>
+        <v>6097</v>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C77">
-        <v>28</v>
+        <v>67</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>6496</v>
+        <v>6098</v>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C78">
-        <v>23</v>
+        <v>44</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>6497</v>
+        <v>6494</v>
       </c>
       <c r="B79">
         <v>1</v>
       </c>
       <c r="C79">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1260,23 +1260,23 @@
         <v>3</v>
       </c>
       <c r="C80">
-        <v>7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>6628</v>
+        <v>6630</v>
       </c>
       <c r="B81">
         <v>3</v>
       </c>
       <c r="C81">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>6927</v>
+        <v>6929</v>
       </c>
       <c r="B82">
         <v>12</v>
@@ -1287,51 +1287,51 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>6929</v>
+        <v>7007</v>
       </c>
       <c r="B83">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C83">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>7318</v>
+        <v>7084</v>
       </c>
       <c r="B84">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C84">
-        <v>9</v>
+        <v>124</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>7520</v>
+        <v>7318</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C85">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>7703</v>
+        <v>7324</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>8104</v>
+        <v>7520</v>
       </c>
       <c r="B87">
         <v>1</v>
@@ -1342,142 +1342,142 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>8106</v>
+        <v>7558</v>
       </c>
       <c r="B88">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C88">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>8121</v>
+        <v>8104</v>
       </c>
       <c r="B89">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C89">
-        <v>330</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>8217</v>
+        <v>8106</v>
       </c>
       <c r="B90">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C90">
-        <v>8</v>
+        <v>42</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>8853</v>
+        <v>8216</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C91">
-        <v>149</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>8898</v>
+        <v>8274</v>
       </c>
       <c r="B92">
         <v>3</v>
       </c>
       <c r="C92">
-        <v>320</v>
+        <v>204</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>8926</v>
+        <v>8284</v>
       </c>
       <c r="B93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C93">
-        <v>34</v>
+        <v>283</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>9135</v>
+        <v>8286</v>
       </c>
       <c r="B94">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C94">
-        <v>7</v>
+        <v>280</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>9208</v>
+        <v>8649</v>
       </c>
       <c r="B95">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C95">
-        <v>55</v>
+        <v>178</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>9289</v>
+        <v>8650</v>
       </c>
       <c r="B96">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C96">
-        <v>71</v>
+        <v>178</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>9577</v>
+        <v>8753</v>
       </c>
       <c r="B97">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C97">
-        <v>7</v>
+        <v>204</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>9778</v>
+        <v>8754</v>
       </c>
       <c r="B98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98">
-        <v>26</v>
+        <v>208</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>9786</v>
+        <v>8756</v>
       </c>
       <c r="B99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C99">
-        <v>40</v>
+        <v>210</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>9789</v>
+        <v>8853</v>
       </c>
       <c r="B100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C100">
         <v>7</v>
@@ -1485,120 +1485,120 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>9828</v>
+        <v>8915</v>
       </c>
       <c r="B101">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C101">
-        <v>7</v>
+        <v>93</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>9829</v>
+        <v>8926</v>
       </c>
       <c r="B102">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C102">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>10105</v>
+        <v>8939</v>
       </c>
       <c r="B103">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C103">
-        <v>7</v>
+        <v>93</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>10491</v>
+        <v>9065</v>
       </c>
       <c r="B104">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C104">
-        <v>7</v>
+        <v>179</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>10716</v>
+        <v>9069</v>
       </c>
       <c r="B105">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C105">
-        <v>59</v>
+        <v>73</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>10719</v>
+        <v>9085</v>
       </c>
       <c r="B106">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="C106">
-        <v>56</v>
+        <v>31</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>10720</v>
+        <v>9135</v>
       </c>
       <c r="B107">
-        <v>80</v>
+        <v>332</v>
       </c>
       <c r="C107">
-        <v>55</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11039</v>
+        <v>9289</v>
       </c>
       <c r="B108">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C108">
-        <v>117</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11044</v>
+        <v>9577</v>
       </c>
       <c r="B109">
-        <v>1</v>
+        <v>332</v>
       </c>
       <c r="C109">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11090</v>
+        <v>9691</v>
       </c>
       <c r="B110">
         <v>1</v>
       </c>
       <c r="C110">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11114</v>
+        <v>9760</v>
       </c>
       <c r="B111">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C111">
         <v>7</v>
@@ -1606,10 +1606,10 @@
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11131</v>
+        <v>9789</v>
       </c>
       <c r="B112">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C112">
         <v>7</v>
@@ -1617,29 +1617,29 @@
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11134</v>
+        <v>9833</v>
       </c>
       <c r="B113">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C113">
-        <v>8</v>
+        <v>74</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11150</v>
+        <v>9910</v>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C114">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11357</v>
+        <v>10105</v>
       </c>
       <c r="B115">
         <v>3</v>
@@ -1650,54 +1650,54 @@
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11493</v>
+        <v>10716</v>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C116">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>11495</v>
+        <v>10825</v>
       </c>
       <c r="B117">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C117">
-        <v>27</v>
+        <v>387</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>11583</v>
+        <v>11134</v>
       </c>
       <c r="B118">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="C118">
-        <v>42</v>
+        <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>11855</v>
+        <v>11150</v>
       </c>
       <c r="B119">
         <v>1</v>
       </c>
       <c r="C119">
-        <v>58</v>
+        <v>26</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>11895</v>
+        <v>11357</v>
       </c>
       <c r="B120">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C120">
         <v>7</v>
@@ -1705,76 +1705,76 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>11914</v>
+        <v>11555</v>
       </c>
       <c r="B121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C121">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>11952</v>
+        <v>11687</v>
       </c>
       <c r="B122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C122">
-        <v>7</v>
+        <v>180</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12128</v>
+        <v>11689</v>
       </c>
       <c r="B123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C123">
-        <v>26</v>
+        <v>181</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12536</v>
+        <v>11885</v>
       </c>
       <c r="B124">
         <v>2</v>
       </c>
       <c r="C124">
-        <v>20</v>
+        <v>115</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12539</v>
+        <v>11886</v>
       </c>
       <c r="B125">
         <v>2</v>
       </c>
       <c r="C125">
-        <v>7</v>
+        <v>115</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12607</v>
+        <v>11914</v>
       </c>
       <c r="B126">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C126">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>12608</v>
+        <v>12128</v>
       </c>
       <c r="B127">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C127">
         <v>7</v>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>12675</v>
+        <v>12539</v>
       </c>
       <c r="B128">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C128">
         <v>7</v>
@@ -1793,18 +1793,18 @@
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>12676</v>
+        <v>12607</v>
       </c>
       <c r="B129">
         <v>3</v>
       </c>
       <c r="C129">
-        <v>62</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>12677</v>
+        <v>12608</v>
       </c>
       <c r="B130">
         <v>3</v>
@@ -1815,109 +1815,109 @@
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>12924</v>
+        <v>12675</v>
       </c>
       <c r="B131">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C131">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>12925</v>
+        <v>12676</v>
       </c>
       <c r="B132">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C132">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>13249</v>
+        <v>12677</v>
       </c>
       <c r="B133">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C133">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>13264</v>
+        <v>12870</v>
       </c>
       <c r="B134">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C134">
-        <v>40</v>
+        <v>136</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>13266</v>
+        <v>12923</v>
       </c>
       <c r="B135">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C135">
-        <v>65</v>
+        <v>21</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>13269</v>
+        <v>12925</v>
       </c>
       <c r="B136">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C136">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>13272</v>
+        <v>13249</v>
       </c>
       <c r="B137">
         <v>29</v>
       </c>
       <c r="C137">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>13467</v>
+        <v>13259</v>
       </c>
       <c r="B138">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C138">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>14017</v>
+        <v>13272</v>
       </c>
       <c r="B139">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C139">
-        <v>7</v>
+        <v>62</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>14018</v>
+        <v>20650</v>
       </c>
       <c r="B140">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C140">
         <v>7</v>
@@ -1925,29 +1925,29 @@
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>19924</v>
+        <v>21082</v>
       </c>
       <c r="B141">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C141">
-        <v>37</v>
+        <v>15</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>21082</v>
+        <v>22049</v>
       </c>
       <c r="B142">
         <v>10</v>
       </c>
       <c r="C142">
-        <v>219</v>
+        <v>10</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>22049</v>
+        <v>22089</v>
       </c>
       <c r="B143">
         <v>10</v>
@@ -1958,79 +1958,57 @@
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>22089</v>
+        <v>23235</v>
       </c>
       <c r="B144">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C144">
-        <v>120</v>
+        <v>48</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>22317</v>
+        <v>23992</v>
       </c>
       <c r="B145">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C145">
-        <v>165</v>
+        <v>24</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>23234</v>
+        <v>24252</v>
       </c>
       <c r="B146">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C146">
-        <v>53</v>
+        <v>119</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>23238</v>
+        <v>24257</v>
       </c>
       <c r="B147">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C147">
-        <v>40</v>
+        <v>84</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>23992</v>
+        <v>24260</v>
       </c>
       <c r="B148">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C148">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3">
-      <c r="A149">
-        <v>24252</v>
-      </c>
-      <c r="B149">
-        <v>1</v>
-      </c>
-      <c r="C149">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3">
-      <c r="A150">
-        <v>24260</v>
-      </c>
-      <c r="B150">
-        <v>1</v>
-      </c>
-      <c r="C150">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_700.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_700.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C148"/>
+  <dimension ref="A1:C146"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -429,1272 +429,1272 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5">
-        <v>108</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6">
-        <v>193</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C7">
-        <v>211</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="B8">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>134</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>29</v>
+        <v>699</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>83</v>
+        <v>141</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10">
-        <v>32</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>88</v>
+        <v>143</v>
       </c>
       <c r="B11">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C11">
-        <v>549</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>94</v>
+        <v>145</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12">
-        <v>71</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>699</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>105</v>
+        <v>159</v>
       </c>
       <c r="B14">
         <v>3</v>
       </c>
       <c r="C14">
-        <v>155</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>114</v>
+        <v>168</v>
       </c>
       <c r="B15">
         <v>3</v>
       </c>
       <c r="C15">
-        <v>156</v>
+        <v>391</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>141</v>
+        <v>202</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16">
-        <v>91</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>143</v>
+        <v>211</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17">
-        <v>90</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>144</v>
+        <v>248</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>90</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
+        <v>305</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
         <v>145</v>
-      </c>
-      <c r="B19">
-        <v>2</v>
-      </c>
-      <c r="C19">
-        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>146</v>
+        <v>307</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20">
-        <v>90</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>159</v>
+        <v>336</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C21">
-        <v>425</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>168</v>
+        <v>345</v>
       </c>
       <c r="B22">
         <v>3</v>
       </c>
       <c r="C22">
-        <v>391</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>211</v>
+        <v>424</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C23">
-        <v>37</v>
+        <v>538</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>216</v>
+        <v>435</v>
       </c>
       <c r="B24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C24">
-        <v>24</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>308</v>
+        <v>436</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25">
-        <v>7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>336</v>
+        <v>470</v>
       </c>
       <c r="B26">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>362</v>
+        <v>590</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C27">
-        <v>82</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>411</v>
+        <v>641</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28">
-        <v>62</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>412</v>
+        <v>949</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C29">
-        <v>79</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>413</v>
+        <v>972</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C30">
-        <v>83</v>
+        <v>353</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>414</v>
+        <v>974</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C31">
-        <v>7</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>436</v>
+        <v>990</v>
       </c>
       <c r="B32">
         <v>2</v>
       </c>
       <c r="C32">
-        <v>59</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>515</v>
+        <v>1070</v>
       </c>
       <c r="B33">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C33">
-        <v>127</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>590</v>
+        <v>1080</v>
       </c>
       <c r="B34">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C34">
-        <v>57</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>949</v>
+        <v>1082</v>
       </c>
       <c r="B35">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>951</v>
+        <v>1447</v>
       </c>
       <c r="B36">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C36">
-        <v>96</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>952</v>
+        <v>1448</v>
       </c>
       <c r="B37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C37">
-        <v>76</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>972</v>
+        <v>1519</v>
       </c>
       <c r="B38">
         <v>3</v>
       </c>
       <c r="C38">
-        <v>353</v>
+        <v>964</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>990</v>
+        <v>1598</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C39">
-        <v>31</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>1070</v>
+        <v>1622</v>
       </c>
       <c r="B40">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C40">
-        <v>19</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>1080</v>
+        <v>1801</v>
       </c>
       <c r="B41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C41">
-        <v>133</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>1082</v>
+        <v>2104</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C42">
-        <v>24</v>
+        <v>197</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>1447</v>
+        <v>2105</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C43">
-        <v>8</v>
+        <v>174</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>1492</v>
+        <v>2109</v>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
       <c r="C44">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>1598</v>
+        <v>2326</v>
       </c>
       <c r="B45">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C45">
-        <v>113</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>1776</v>
+        <v>2331</v>
       </c>
       <c r="B46">
         <v>1</v>
       </c>
       <c r="C46">
-        <v>64</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>1801</v>
+        <v>2438</v>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47">
-        <v>95</v>
+        <v>620</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2049</v>
+        <v>2859</v>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C48">
-        <v>323</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2057</v>
+        <v>2912</v>
       </c>
       <c r="B49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C49">
-        <v>277</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2108</v>
+        <v>2991</v>
       </c>
       <c r="B50">
         <v>3</v>
       </c>
       <c r="C50">
-        <v>154</v>
+        <v>139</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2109</v>
+        <v>3016</v>
       </c>
       <c r="B51">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C51">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2328</v>
+        <v>3021</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C52">
-        <v>128</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>2331</v>
+        <v>3434</v>
       </c>
       <c r="B53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53">
-        <v>70</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>2422</v>
+        <v>3454</v>
       </c>
       <c r="B54">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C54">
-        <v>109</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>2726</v>
+        <v>3671</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C55">
-        <v>76</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>2859</v>
+        <v>3840</v>
       </c>
       <c r="B56">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C56">
-        <v>42</v>
+        <v>101</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>2879</v>
+        <v>3909</v>
       </c>
       <c r="B57">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C57">
-        <v>22</v>
+        <v>278</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>2912</v>
+        <v>4076</v>
       </c>
       <c r="B58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C58">
-        <v>28</v>
+        <v>117</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>2916</v>
+        <v>4178</v>
       </c>
       <c r="B59">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C59">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>2991</v>
+        <v>4246</v>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C60">
-        <v>139</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>3454</v>
+        <v>4957</v>
       </c>
       <c r="B61">
-        <v>1</v>
+        <v>332</v>
       </c>
       <c r="C61">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3577</v>
+        <v>4960</v>
       </c>
       <c r="B62">
-        <v>25</v>
+        <v>332</v>
       </c>
       <c r="C62">
-        <v>52</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>4246</v>
+        <v>5165</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C63">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>5151</v>
+        <v>5208</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C64">
-        <v>14</v>
+        <v>331</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5165</v>
+        <v>5209</v>
       </c>
       <c r="B65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C65">
-        <v>28</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5208</v>
+        <v>5243</v>
       </c>
       <c r="B66">
         <v>3</v>
       </c>
       <c r="C66">
-        <v>331</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5243</v>
+        <v>5435</v>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C67">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5435</v>
+        <v>5493</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C68">
-        <v>28</v>
+        <v>60</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5490</v>
+        <v>5513</v>
       </c>
       <c r="B69">
         <v>2</v>
       </c>
       <c r="C69">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5491</v>
+        <v>5584</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C70">
-        <v>60</v>
+        <v>154</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5493</v>
+        <v>5723</v>
       </c>
       <c r="B71">
         <v>2</v>
       </c>
       <c r="C71">
-        <v>60</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5494</v>
+        <v>5966</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72">
-        <v>59</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5513</v>
+        <v>5967</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73">
-        <v>48</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5723</v>
+        <v>6034</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C74">
-        <v>37</v>
+        <v>391</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>5966</v>
+        <v>6097</v>
       </c>
       <c r="B75">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C75">
-        <v>7</v>
+        <v>67</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>5967</v>
+        <v>6494</v>
       </c>
       <c r="B76">
         <v>1</v>
       </c>
       <c r="C76">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>6097</v>
+        <v>6540</v>
       </c>
       <c r="B77">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="C77">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>6098</v>
+        <v>6630</v>
       </c>
       <c r="B78">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C78">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>6494</v>
+        <v>6929</v>
       </c>
       <c r="B79">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C79">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>6627</v>
+        <v>7036</v>
       </c>
       <c r="B80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C80">
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>6630</v>
+        <v>7318</v>
       </c>
       <c r="B81">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C81">
-        <v>59</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>6929</v>
+        <v>8104</v>
       </c>
       <c r="B82">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C82">
-        <v>7</v>
+        <v>114</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>7007</v>
+        <v>8216</v>
       </c>
       <c r="B83">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C83">
-        <v>47</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>7084</v>
+        <v>8217</v>
       </c>
       <c r="B84">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C84">
-        <v>124</v>
+        <v>13</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>7318</v>
+        <v>8284</v>
       </c>
       <c r="B85">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C85">
-        <v>7</v>
+        <v>296</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>7324</v>
+        <v>8753</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86">
-        <v>36</v>
+        <v>212</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>7520</v>
+        <v>8756</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C87">
-        <v>7</v>
+        <v>212</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>7558</v>
+        <v>8938</v>
       </c>
       <c r="B88">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C88">
-        <v>39</v>
+        <v>92</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>8104</v>
+        <v>9069</v>
       </c>
       <c r="B89">
         <v>1</v>
       </c>
       <c r="C89">
-        <v>7</v>
+        <v>74</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>8106</v>
+        <v>9085</v>
       </c>
       <c r="B90">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C90">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>8216</v>
+        <v>9135</v>
       </c>
       <c r="B91">
-        <v>10</v>
+        <v>332</v>
       </c>
       <c r="C91">
-        <v>1245</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>8274</v>
+        <v>9577</v>
       </c>
       <c r="B92">
-        <v>3</v>
+        <v>332</v>
       </c>
       <c r="C92">
-        <v>204</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>8284</v>
+        <v>9691</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C93">
-        <v>283</v>
+        <v>44</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>8286</v>
+        <v>9789</v>
       </c>
       <c r="B94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C94">
-        <v>280</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>8649</v>
+        <v>9829</v>
       </c>
       <c r="B95">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C95">
-        <v>178</v>
+        <v>68</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>8650</v>
+        <v>9833</v>
       </c>
       <c r="B96">
         <v>2</v>
       </c>
       <c r="C96">
-        <v>178</v>
+        <v>74</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>8753</v>
+        <v>9910</v>
       </c>
       <c r="B97">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C97">
-        <v>204</v>
+        <v>42</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>8754</v>
+        <v>10105</v>
       </c>
       <c r="B98">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C98">
-        <v>208</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>8756</v>
+        <v>10491</v>
       </c>
       <c r="B99">
-        <v>2</v>
+        <v>332</v>
       </c>
       <c r="C99">
-        <v>210</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>8853</v>
+        <v>10529</v>
       </c>
       <c r="B100">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C100">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>8915</v>
+        <v>10716</v>
       </c>
       <c r="B101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C101">
-        <v>93</v>
+        <v>59</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>8926</v>
+        <v>10993</v>
       </c>
       <c r="B102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C102">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>8939</v>
+        <v>11044</v>
       </c>
       <c r="B103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C103">
-        <v>93</v>
+        <v>28</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>9065</v>
+        <v>11134</v>
       </c>
       <c r="B104">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C104">
-        <v>179</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>9069</v>
+        <v>11150</v>
       </c>
       <c r="B105">
         <v>1</v>
       </c>
       <c r="C105">
-        <v>73</v>
+        <v>26</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>9085</v>
+        <v>11357</v>
       </c>
       <c r="B106">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C106">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>9135</v>
+        <v>11467</v>
       </c>
       <c r="B107">
-        <v>332</v>
+        <v>1</v>
       </c>
       <c r="C107">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>9289</v>
+        <v>11510</v>
       </c>
       <c r="B108">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C108">
-        <v>7</v>
+        <v>353</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>9577</v>
+        <v>11687</v>
       </c>
       <c r="B109">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C109">
-        <v>7</v>
+        <v>186</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>9691</v>
+        <v>11689</v>
       </c>
       <c r="B110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C110">
-        <v>44</v>
+        <v>186</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>9760</v>
+        <v>11690</v>
       </c>
       <c r="B111">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C111">
-        <v>7</v>
+        <v>186</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>9789</v>
+        <v>11711</v>
       </c>
       <c r="B112">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C112">
-        <v>7</v>
+        <v>191</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>9833</v>
+        <v>11739</v>
       </c>
       <c r="B113">
         <v>2</v>
       </c>
       <c r="C113">
-        <v>74</v>
+        <v>35</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>9910</v>
+        <v>11885</v>
       </c>
       <c r="B114">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C114">
-        <v>42</v>
+        <v>114</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>10105</v>
+        <v>11886</v>
       </c>
       <c r="B115">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C115">
-        <v>7</v>
+        <v>114</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>10716</v>
+        <v>11961</v>
       </c>
       <c r="B116">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C116">
-        <v>59</v>
+        <v>33</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>10825</v>
+        <v>12128</v>
       </c>
       <c r="B117">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C117">
-        <v>387</v>
+        <v>27</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>11134</v>
+        <v>12539</v>
       </c>
       <c r="B118">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C118">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>11150</v>
+        <v>12607</v>
       </c>
       <c r="B119">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C119">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>11357</v>
+        <v>12608</v>
       </c>
       <c r="B120">
         <v>3</v>
@@ -1705,76 +1705,76 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>11555</v>
+        <v>12675</v>
       </c>
       <c r="B121">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C121">
-        <v>77</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>11687</v>
+        <v>12676</v>
       </c>
       <c r="B122">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C122">
-        <v>180</v>
+        <v>68</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>11689</v>
+        <v>12677</v>
       </c>
       <c r="B123">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C123">
-        <v>181</v>
+        <v>71</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>11885</v>
+        <v>12870</v>
       </c>
       <c r="B124">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C124">
-        <v>115</v>
+        <v>136</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>11886</v>
+        <v>12925</v>
       </c>
       <c r="B125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C125">
-        <v>115</v>
+        <v>37</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>11914</v>
+        <v>13259</v>
       </c>
       <c r="B126">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C126">
-        <v>47</v>
+        <v>21</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>12128</v>
+        <v>13266</v>
       </c>
       <c r="B127">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C127">
         <v>7</v>
@@ -1782,21 +1782,21 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>12539</v>
+        <v>13280</v>
       </c>
       <c r="B128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C128">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>12607</v>
+        <v>13467</v>
       </c>
       <c r="B129">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C129">
         <v>7</v>
@@ -1804,43 +1804,43 @@
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>12608</v>
+        <v>13962</v>
       </c>
       <c r="B130">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C130">
-        <v>7</v>
+        <v>96</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>12675</v>
+        <v>13968</v>
       </c>
       <c r="B131">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C131">
-        <v>7</v>
+        <v>154</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>12676</v>
+        <v>19685</v>
       </c>
       <c r="B132">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C132">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>12677</v>
+        <v>20650</v>
       </c>
       <c r="B133">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C133">
         <v>7</v>
@@ -1848,167 +1848,145 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>12870</v>
+        <v>21082</v>
       </c>
       <c r="B134">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C134">
-        <v>136</v>
+        <v>15</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>12923</v>
+        <v>21699</v>
       </c>
       <c r="B135">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C135">
-        <v>21</v>
+        <v>107</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>12925</v>
+        <v>21798</v>
       </c>
       <c r="B136">
         <v>1</v>
       </c>
       <c r="C136">
-        <v>37</v>
+        <v>84</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>13249</v>
+        <v>22049</v>
       </c>
       <c r="B137">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C137">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>13259</v>
+        <v>22089</v>
       </c>
       <c r="B138">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C138">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>13272</v>
+        <v>22313</v>
       </c>
       <c r="B139">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C139">
-        <v>62</v>
+        <v>40</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>20650</v>
+        <v>22316</v>
       </c>
       <c r="B140">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C140">
-        <v>7</v>
+        <v>184</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>21082</v>
+        <v>23235</v>
       </c>
       <c r="B141">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C141">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>22049</v>
+        <v>23992</v>
       </c>
       <c r="B142">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C142">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>22089</v>
+        <v>24252</v>
       </c>
       <c r="B143">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C143">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>23235</v>
+        <v>24257</v>
       </c>
       <c r="B144">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C144">
-        <v>48</v>
+        <v>84</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>23992</v>
+        <v>24260</v>
       </c>
       <c r="B145">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C145">
-        <v>24</v>
+        <v>83</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>24252</v>
+        <v>24705</v>
       </c>
       <c r="B146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C146">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3">
-      <c r="A147">
-        <v>24257</v>
-      </c>
-      <c r="B147">
-        <v>1</v>
-      </c>
-      <c r="C147">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3">
-      <c r="A148">
-        <v>24260</v>
-      </c>
-      <c r="B148">
-        <v>1</v>
-      </c>
-      <c r="C148">
-        <v>83</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_700.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_700.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C146"/>
+  <dimension ref="A1:C149"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,13 +396,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -413,7 +413,7 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -424,7 +424,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>111</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -435,7 +435,7 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>133</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -451,24 +451,24 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7">
-        <v>134</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>32</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -484,29 +484,29 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10">
-        <v>91</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>90</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -517,7 +517,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B13">
         <v>2</v>
@@ -528,95 +528,95 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>10</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>391</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>202</v>
+        <v>145</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16">
-        <v>42</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>211</v>
+        <v>152</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C17">
-        <v>37</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>248</v>
+        <v>159</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19">
-        <v>145</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>307</v>
+        <v>168</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20">
-        <v>144</v>
+        <v>391</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>336</v>
+        <v>170</v>
       </c>
       <c r="B21">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C21">
-        <v>65</v>
+        <v>211</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>345</v>
+        <v>201</v>
       </c>
       <c r="B22">
         <v>3</v>
@@ -627,483 +627,483 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>424</v>
+        <v>205</v>
       </c>
       <c r="B23">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C23">
-        <v>538</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>435</v>
+        <v>211</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24">
-        <v>59</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>436</v>
+        <v>216</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C25">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>470</v>
+        <v>307</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26">
-        <v>34</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>590</v>
+        <v>336</v>
       </c>
       <c r="B27">
         <v>15</v>
       </c>
       <c r="C27">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>641</v>
+        <v>409</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28">
-        <v>7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>949</v>
+        <v>411</v>
       </c>
       <c r="B29">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C29">
-        <v>7</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>972</v>
+        <v>413</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>353</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>974</v>
+        <v>417</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C31">
-        <v>90</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>990</v>
+        <v>418</v>
       </c>
       <c r="B32">
         <v>2</v>
       </c>
       <c r="C32">
-        <v>31</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1070</v>
+        <v>434</v>
       </c>
       <c r="B33">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>19</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1080</v>
+        <v>435</v>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C34">
-        <v>133</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1082</v>
+        <v>589</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35">
-        <v>25</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1447</v>
+        <v>624</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36">
-        <v>8</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1448</v>
+        <v>944</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C37">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1519</v>
+        <v>949</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C38">
-        <v>964</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>1598</v>
+        <v>950</v>
       </c>
       <c r="B39">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C39">
-        <v>113</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>1622</v>
+        <v>990</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>1801</v>
+        <v>1070</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C41">
-        <v>60</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2104</v>
+        <v>1120</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C42">
-        <v>197</v>
+        <v>65</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2105</v>
+        <v>1134</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C43">
-        <v>174</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2109</v>
+        <v>1413</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C44">
-        <v>22</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2326</v>
+        <v>1447</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C45">
-        <v>57</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2331</v>
+        <v>1492</v>
       </c>
       <c r="B46">
         <v>1</v>
       </c>
       <c r="C46">
-        <v>73</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2438</v>
+        <v>1598</v>
       </c>
       <c r="B47">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C47">
-        <v>620</v>
+        <v>113</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2859</v>
+        <v>1656</v>
       </c>
       <c r="B48">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C48">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2912</v>
+        <v>2108</v>
       </c>
       <c r="B49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C49">
-        <v>28</v>
+        <v>252</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2991</v>
+        <v>2109</v>
       </c>
       <c r="B50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>139</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>3016</v>
+        <v>2188</v>
       </c>
       <c r="B51">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C51">
-        <v>30</v>
+        <v>475</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>3021</v>
+        <v>2322</v>
       </c>
       <c r="B52">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C52">
-        <v>42</v>
+        <v>65</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>3434</v>
+        <v>2331</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53">
-        <v>53</v>
+        <v>73</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>3454</v>
+        <v>2912</v>
       </c>
       <c r="B54">
         <v>1</v>
       </c>
       <c r="C54">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3671</v>
+        <v>3016</v>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C55">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3840</v>
+        <v>3258</v>
       </c>
       <c r="B56">
         <v>1</v>
       </c>
       <c r="C56">
-        <v>101</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3909</v>
+        <v>3434</v>
       </c>
       <c r="B57">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C57">
-        <v>278</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>4076</v>
+        <v>3454</v>
       </c>
       <c r="B58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C58">
-        <v>117</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>4178</v>
+        <v>3671</v>
       </c>
       <c r="B59">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C59">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>4246</v>
+        <v>3840</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60">
-        <v>7</v>
+        <v>99</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>4957</v>
+        <v>3909</v>
       </c>
       <c r="B61">
-        <v>332</v>
+        <v>7</v>
       </c>
       <c r="C61">
-        <v>15</v>
+        <v>234</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>4960</v>
+        <v>3980</v>
       </c>
       <c r="B62">
-        <v>332</v>
+        <v>4</v>
       </c>
       <c r="C62">
-        <v>26</v>
+        <v>470</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>5165</v>
+        <v>3982</v>
       </c>
       <c r="B63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C63">
-        <v>28</v>
+        <v>776</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>5208</v>
+        <v>4019</v>
       </c>
       <c r="B64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C64">
-        <v>331</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5209</v>
+        <v>4223</v>
       </c>
       <c r="B65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C65">
-        <v>331</v>
+        <v>38</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5243</v>
+        <v>4246</v>
       </c>
       <c r="B66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C66">
         <v>7</v>
@@ -1111,76 +1111,76 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5435</v>
+        <v>4955</v>
       </c>
       <c r="B67">
-        <v>1</v>
+        <v>332</v>
       </c>
       <c r="C67">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5493</v>
+        <v>5081</v>
       </c>
       <c r="B68">
         <v>2</v>
       </c>
       <c r="C68">
-        <v>60</v>
+        <v>184</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5513</v>
+        <v>5086</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69">
-        <v>48</v>
+        <v>170</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5584</v>
+        <v>5152</v>
       </c>
       <c r="B70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C70">
-        <v>154</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5723</v>
+        <v>5165</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C71">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5966</v>
+        <v>5208</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C72">
-        <v>7</v>
+        <v>534</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5967</v>
+        <v>5243</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C73">
         <v>7</v>
@@ -1188,87 +1188,87 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>6034</v>
+        <v>5435</v>
       </c>
       <c r="B74">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C74">
-        <v>391</v>
+        <v>28</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>6097</v>
+        <v>5490</v>
       </c>
       <c r="B75">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C75">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>6494</v>
+        <v>5491</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76">
-        <v>29</v>
+        <v>57</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>6540</v>
+        <v>5494</v>
       </c>
       <c r="B77">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C77">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>6630</v>
+        <v>5513</v>
       </c>
       <c r="B78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C78">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>6929</v>
+        <v>5584</v>
       </c>
       <c r="B79">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C79">
-        <v>7</v>
+        <v>153</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>7036</v>
+        <v>5966</v>
       </c>
       <c r="B80">
         <v>1</v>
       </c>
       <c r="C80">
-        <v>74</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>7318</v>
+        <v>5967</v>
       </c>
       <c r="B81">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C81">
         <v>7</v>
@@ -1276,109 +1276,109 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>8104</v>
+        <v>6097</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C82">
-        <v>114</v>
+        <v>66</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>8216</v>
+        <v>6098</v>
       </c>
       <c r="B83">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="C83">
-        <v>1245</v>
+        <v>44</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>8217</v>
+        <v>6494</v>
       </c>
       <c r="B84">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>8284</v>
+        <v>6496</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>296</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>8753</v>
+        <v>6497</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>212</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>8756</v>
+        <v>6540</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C87">
-        <v>212</v>
+        <v>75</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>8938</v>
+        <v>6630</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C88">
-        <v>92</v>
+        <v>61</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>9069</v>
+        <v>6927</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C89">
-        <v>74</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>9085</v>
+        <v>6929</v>
       </c>
       <c r="B90">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C90">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>9135</v>
+        <v>7318</v>
       </c>
       <c r="B91">
-        <v>332</v>
+        <v>12</v>
       </c>
       <c r="C91">
         <v>7</v>
@@ -1386,315 +1386,315 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>9577</v>
+        <v>7520</v>
       </c>
       <c r="B92">
-        <v>332</v>
+        <v>1</v>
       </c>
       <c r="C92">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>9691</v>
+        <v>8104</v>
       </c>
       <c r="B93">
         <v>1</v>
       </c>
       <c r="C93">
-        <v>44</v>
+        <v>192</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>9789</v>
+        <v>8106</v>
       </c>
       <c r="B94">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C94">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>9829</v>
+        <v>8216</v>
       </c>
       <c r="B95">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C95">
-        <v>68</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>9833</v>
+        <v>8284</v>
       </c>
       <c r="B96">
         <v>2</v>
       </c>
       <c r="C96">
-        <v>74</v>
+        <v>295</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>9910</v>
+        <v>8286</v>
       </c>
       <c r="B97">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C97">
-        <v>42</v>
+        <v>295</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>10105</v>
+        <v>8648</v>
       </c>
       <c r="B98">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C98">
-        <v>7</v>
+        <v>107</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>10491</v>
+        <v>8649</v>
       </c>
       <c r="B99">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C99">
-        <v>7</v>
+        <v>178</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>10529</v>
+        <v>8672</v>
       </c>
       <c r="B100">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C100">
-        <v>40</v>
+        <v>168</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>10716</v>
+        <v>8675</v>
       </c>
       <c r="B101">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C101">
-        <v>59</v>
+        <v>168</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>10993</v>
+        <v>8677</v>
       </c>
       <c r="B102">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C102">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>11044</v>
+        <v>8753</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C103">
-        <v>28</v>
+        <v>212</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>11134</v>
+        <v>8756</v>
       </c>
       <c r="B104">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C104">
-        <v>8</v>
+        <v>212</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>11150</v>
+        <v>8939</v>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C105">
-        <v>26</v>
+        <v>93</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11357</v>
+        <v>8944</v>
       </c>
       <c r="B106">
         <v>3</v>
       </c>
       <c r="C106">
-        <v>7</v>
+        <v>130</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11467</v>
+        <v>9065</v>
       </c>
       <c r="B107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C107">
-        <v>60</v>
+        <v>186</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11510</v>
+        <v>9085</v>
       </c>
       <c r="B108">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C108">
-        <v>353</v>
+        <v>31</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11687</v>
+        <v>9577</v>
       </c>
       <c r="B109">
-        <v>2</v>
+        <v>332</v>
       </c>
       <c r="C109">
-        <v>186</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11689</v>
+        <v>9789</v>
       </c>
       <c r="B110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C110">
-        <v>186</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11690</v>
+        <v>9833</v>
       </c>
       <c r="B111">
         <v>2</v>
       </c>
       <c r="C111">
-        <v>186</v>
+        <v>74</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11711</v>
+        <v>9910</v>
       </c>
       <c r="B112">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C112">
-        <v>191</v>
+        <v>42</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11739</v>
+        <v>10105</v>
       </c>
       <c r="B113">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C113">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11885</v>
+        <v>10529</v>
       </c>
       <c r="B114">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C114">
-        <v>114</v>
+        <v>40</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11886</v>
+        <v>10993</v>
       </c>
       <c r="B115">
         <v>2</v>
       </c>
       <c r="C115">
-        <v>114</v>
+        <v>32</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11961</v>
+        <v>11114</v>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C116">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>12128</v>
+        <v>11131</v>
       </c>
       <c r="B117">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C117">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>12539</v>
+        <v>11134</v>
       </c>
       <c r="B118">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C118">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12607</v>
+        <v>11150</v>
       </c>
       <c r="B119">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C119">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12608</v>
+        <v>11357</v>
       </c>
       <c r="B120">
         <v>3</v>
@@ -1705,98 +1705,98 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12675</v>
+        <v>11396</v>
       </c>
       <c r="B121">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C121">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12676</v>
+        <v>11555</v>
       </c>
       <c r="B122">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C122">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12677</v>
+        <v>11687</v>
       </c>
       <c r="B123">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C123">
-        <v>71</v>
+        <v>186</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12870</v>
+        <v>11689</v>
       </c>
       <c r="B124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C124">
-        <v>136</v>
+        <v>186</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12925</v>
+        <v>11690</v>
       </c>
       <c r="B125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C125">
-        <v>37</v>
+        <v>186</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>13259</v>
+        <v>11794</v>
       </c>
       <c r="B126">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C126">
-        <v>21</v>
+        <v>94</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>13266</v>
+        <v>12128</v>
       </c>
       <c r="B127">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C127">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>13280</v>
+        <v>12539</v>
       </c>
       <c r="B128">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C128">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>13467</v>
+        <v>12607</v>
       </c>
       <c r="B129">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C129">
         <v>7</v>
@@ -1804,43 +1804,43 @@
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>13962</v>
+        <v>12608</v>
       </c>
       <c r="B130">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C130">
-        <v>96</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>13968</v>
+        <v>12675</v>
       </c>
       <c r="B131">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C131">
-        <v>154</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>19685</v>
+        <v>12676</v>
       </c>
       <c r="B132">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C132">
-        <v>20</v>
+        <v>69</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>20650</v>
+        <v>12677</v>
       </c>
       <c r="B133">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C133">
         <v>7</v>
@@ -1848,145 +1848,178 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>21082</v>
+        <v>12870</v>
       </c>
       <c r="B134">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C134">
-        <v>15</v>
+        <v>136</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>21699</v>
+        <v>12923</v>
       </c>
       <c r="B135">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C135">
-        <v>107</v>
+        <v>35</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>21798</v>
+        <v>12925</v>
       </c>
       <c r="B136">
         <v>1</v>
       </c>
       <c r="C136">
-        <v>84</v>
+        <v>37</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>22049</v>
+        <v>13259</v>
       </c>
       <c r="B137">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C137">
-        <v>10</v>
+        <v>34</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>22089</v>
+        <v>13962</v>
       </c>
       <c r="B138">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C138">
-        <v>10</v>
+        <v>58</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>22313</v>
+        <v>20650</v>
       </c>
       <c r="B139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C139">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>22316</v>
+        <v>21082</v>
       </c>
       <c r="B140">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C140">
-        <v>184</v>
+        <v>15</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>23235</v>
+        <v>21793</v>
       </c>
       <c r="B141">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C141">
-        <v>48</v>
+        <v>414</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>23992</v>
+        <v>22089</v>
       </c>
       <c r="B142">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C142">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>24252</v>
+        <v>22317</v>
       </c>
       <c r="B143">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C143">
-        <v>7</v>
+        <v>184</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>24257</v>
+        <v>23235</v>
       </c>
       <c r="B144">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C144">
-        <v>84</v>
+        <v>48</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>24260</v>
+        <v>23992</v>
       </c>
       <c r="B145">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C145">
-        <v>83</v>
+        <v>24</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>24705</v>
+        <v>24252</v>
       </c>
       <c r="B146">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C146">
-        <v>173</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147">
+        <v>24257</v>
+      </c>
+      <c r="B147">
+        <v>1</v>
+      </c>
+      <c r="C147">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148">
+        <v>24258</v>
+      </c>
+      <c r="B148">
+        <v>1</v>
+      </c>
+      <c r="C148">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149">
+        <v>24260</v>
+      </c>
+      <c r="B149">
+        <v>1</v>
+      </c>
+      <c r="C149">
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_700.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_700.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C149"/>
+  <dimension ref="A1:C143"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -418,95 +418,95 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>66</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5">
-        <v>66</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>110</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="B7">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>74</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>72</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>699</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>27</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11">
-        <v>156</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -517,373 +517,373 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C13">
-        <v>90</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14">
-        <v>90</v>
+        <v>439</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15">
-        <v>90</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16">
-        <v>90</v>
+        <v>310</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>152</v>
+        <v>307</v>
       </c>
       <c r="B17">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C17">
-        <v>119</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>159</v>
+        <v>308</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>10</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>167</v>
+        <v>336</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C19">
-        <v>219</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>168</v>
+        <v>410</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>391</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>170</v>
+        <v>414</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>211</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>201</v>
+        <v>475</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C22">
-        <v>190</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>205</v>
+        <v>515</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C23">
-        <v>63</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>211</v>
+        <v>524</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>216</v>
+        <v>590</v>
       </c>
       <c r="B25">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C25">
-        <v>24</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>307</v>
+        <v>641</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>144</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>336</v>
+        <v>903</v>
       </c>
       <c r="B27">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C27">
-        <v>65</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>409</v>
+        <v>924</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>411</v>
+        <v>926</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>62</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>413</v>
+        <v>972</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C30">
-        <v>83</v>
+        <v>353</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>417</v>
+        <v>974</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C31">
-        <v>7</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>418</v>
+        <v>1082</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32">
-        <v>82</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>434</v>
+        <v>1124</v>
       </c>
       <c r="B33">
         <v>2</v>
       </c>
       <c r="C33">
-        <v>59</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>435</v>
+        <v>1243</v>
       </c>
       <c r="B34">
         <v>2</v>
       </c>
       <c r="C34">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>589</v>
+        <v>1309</v>
       </c>
       <c r="B35">
         <v>2</v>
       </c>
       <c r="C35">
-        <v>79</v>
+        <v>381</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>624</v>
+        <v>1447</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36">
-        <v>58</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>944</v>
+        <v>1598</v>
       </c>
       <c r="B37">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="C37">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>949</v>
+        <v>1602</v>
       </c>
       <c r="B38">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>950</v>
+        <v>1880</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C39">
-        <v>34</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>990</v>
+        <v>2049</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C40">
-        <v>52</v>
+        <v>323</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>1070</v>
+        <v>2109</v>
       </c>
       <c r="B41">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C41">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>1120</v>
+        <v>2188</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42">
-        <v>65</v>
+        <v>485</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>1134</v>
+        <v>2322</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43">
-        <v>25</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>1413</v>
+        <v>2326</v>
       </c>
       <c r="B44">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>1447</v>
+        <v>2331</v>
       </c>
       <c r="B45">
         <v>1</v>
       </c>
       <c r="C45">
-        <v>8</v>
+        <v>73</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>1492</v>
+        <v>2419</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C46">
         <v>21</v>
@@ -891,483 +891,483 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>1598</v>
+        <v>2423</v>
       </c>
       <c r="B47">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C47">
-        <v>113</v>
+        <v>145</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>1656</v>
+        <v>2424</v>
       </c>
       <c r="B48">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C48">
-        <v>7</v>
+        <v>135</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2108</v>
+        <v>2438</v>
       </c>
       <c r="B49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C49">
-        <v>252</v>
+        <v>744</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2109</v>
+        <v>3016</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C50">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2188</v>
+        <v>3454</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51">
-        <v>475</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2322</v>
+        <v>3477</v>
       </c>
       <c r="B52">
         <v>2</v>
       </c>
       <c r="C52">
-        <v>65</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>2331</v>
+        <v>3577</v>
       </c>
       <c r="B53">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C53">
-        <v>73</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>2912</v>
+        <v>3673</v>
       </c>
       <c r="B54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>28</v>
+        <v>144</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3016</v>
+        <v>3982</v>
       </c>
       <c r="B55">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="C55">
-        <v>30</v>
+        <v>459</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3258</v>
+        <v>4955</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>332</v>
       </c>
       <c r="C56">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3434</v>
+        <v>4957</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>332</v>
       </c>
       <c r="C57">
-        <v>53</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3454</v>
+        <v>4960</v>
       </c>
       <c r="B58">
-        <v>1</v>
+        <v>332</v>
       </c>
       <c r="C58">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3671</v>
+        <v>5081</v>
       </c>
       <c r="B59">
         <v>2</v>
       </c>
       <c r="C59">
-        <v>50</v>
+        <v>108</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3840</v>
+        <v>5152</v>
       </c>
       <c r="B60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60">
-        <v>99</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>3909</v>
+        <v>5243</v>
       </c>
       <c r="B61">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C61">
-        <v>234</v>
+        <v>146</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3980</v>
+        <v>5341</v>
       </c>
       <c r="B62">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C62">
-        <v>470</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>3982</v>
+        <v>5647</v>
       </c>
       <c r="B63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C63">
-        <v>776</v>
+        <v>36</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>4019</v>
+        <v>5652</v>
       </c>
       <c r="B64">
         <v>2</v>
       </c>
       <c r="C64">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>4223</v>
+        <v>5654</v>
       </c>
       <c r="B65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C65">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>4246</v>
+        <v>5733</v>
       </c>
       <c r="B66">
         <v>2</v>
       </c>
       <c r="C66">
-        <v>7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>4955</v>
+        <v>5966</v>
       </c>
       <c r="B67">
-        <v>332</v>
+        <v>1</v>
       </c>
       <c r="C67">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5081</v>
+        <v>5967</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68">
-        <v>184</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5086</v>
+        <v>6097</v>
       </c>
       <c r="B69">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C69">
-        <v>170</v>
+        <v>81</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5152</v>
+        <v>6098</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C70">
-        <v>23</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5165</v>
+        <v>6158</v>
       </c>
       <c r="B71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C71">
-        <v>28</v>
+        <v>305</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5208</v>
+        <v>6575</v>
       </c>
       <c r="B72">
         <v>3</v>
       </c>
       <c r="C72">
-        <v>534</v>
+        <v>314</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5243</v>
+        <v>7885</v>
       </c>
       <c r="B73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C73">
-        <v>7</v>
+        <v>82</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5435</v>
+        <v>7886</v>
       </c>
       <c r="B74">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C74">
-        <v>28</v>
+        <v>84</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>5490</v>
+        <v>8104</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C75">
-        <v>60</v>
+        <v>119</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>5491</v>
+        <v>8217</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C76">
-        <v>57</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>5494</v>
+        <v>8283</v>
       </c>
       <c r="B77">
         <v>2</v>
       </c>
       <c r="C77">
-        <v>60</v>
+        <v>295</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>5513</v>
+        <v>8284</v>
       </c>
       <c r="B78">
         <v>2</v>
       </c>
       <c r="C78">
-        <v>48</v>
+        <v>295</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>5584</v>
+        <v>8286</v>
       </c>
       <c r="B79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C79">
-        <v>153</v>
+        <v>295</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>5966</v>
+        <v>8635</v>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C80">
-        <v>7</v>
+        <v>205</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>5967</v>
+        <v>8753</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81">
-        <v>7</v>
+        <v>212</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>6097</v>
+        <v>8943</v>
       </c>
       <c r="B82">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C82">
-        <v>66</v>
+        <v>225</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>6098</v>
+        <v>9577</v>
       </c>
       <c r="B83">
-        <v>80</v>
+        <v>332</v>
       </c>
       <c r="C83">
-        <v>44</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>6494</v>
+        <v>9789</v>
       </c>
       <c r="B84">
         <v>1</v>
       </c>
       <c r="C84">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>6496</v>
+        <v>10105</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C85">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>6497</v>
+        <v>10149</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C86">
-        <v>22</v>
+        <v>736</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>6540</v>
+        <v>10465</v>
       </c>
       <c r="B87">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C87">
-        <v>75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>6630</v>
+        <v>10529</v>
       </c>
       <c r="B88">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C88">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>6927</v>
+        <v>10716</v>
       </c>
       <c r="B89">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C89">
-        <v>10</v>
+        <v>57</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>6929</v>
+        <v>10780</v>
       </c>
       <c r="B90">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C90">
         <v>7</v>
@@ -1375,249 +1375,249 @@
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>7318</v>
+        <v>10825</v>
       </c>
       <c r="B91">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C91">
-        <v>7</v>
+        <v>400</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>7520</v>
+        <v>11081</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C92">
-        <v>12</v>
+        <v>216</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>8104</v>
+        <v>11093</v>
       </c>
       <c r="B93">
         <v>1</v>
       </c>
       <c r="C93">
-        <v>192</v>
+        <v>61</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>8106</v>
+        <v>11116</v>
       </c>
       <c r="B94">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C94">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>8216</v>
+        <v>11134</v>
       </c>
       <c r="B95">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C95">
-        <v>1245</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>8284</v>
+        <v>11150</v>
       </c>
       <c r="B96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C96">
-        <v>295</v>
+        <v>26</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>8286</v>
+        <v>11357</v>
       </c>
       <c r="B97">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C97">
-        <v>295</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>8648</v>
+        <v>11404</v>
       </c>
       <c r="B98">
         <v>2</v>
       </c>
       <c r="C98">
-        <v>107</v>
+        <v>67</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>8649</v>
+        <v>11492</v>
       </c>
       <c r="B99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C99">
-        <v>178</v>
+        <v>53</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>8672</v>
+        <v>11493</v>
       </c>
       <c r="B100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C100">
-        <v>168</v>
+        <v>26</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>8675</v>
+        <v>11555</v>
       </c>
       <c r="B101">
         <v>2</v>
       </c>
       <c r="C101">
-        <v>168</v>
+        <v>76</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>8677</v>
+        <v>11687</v>
       </c>
       <c r="B102">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C102">
-        <v>8</v>
+        <v>186</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>8753</v>
+        <v>11885</v>
       </c>
       <c r="B103">
         <v>2</v>
       </c>
       <c r="C103">
-        <v>212</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>8756</v>
+        <v>11886</v>
       </c>
       <c r="B104">
         <v>2</v>
       </c>
       <c r="C104">
-        <v>212</v>
+        <v>114</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>8939</v>
+        <v>11914</v>
       </c>
       <c r="B105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C105">
-        <v>93</v>
+        <v>47</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>8944</v>
+        <v>11967</v>
       </c>
       <c r="B106">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C106">
-        <v>130</v>
+        <v>79</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>9065</v>
+        <v>11969</v>
       </c>
       <c r="B107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C107">
-        <v>186</v>
+        <v>44</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>9085</v>
+        <v>11971</v>
       </c>
       <c r="B108">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C108">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>9577</v>
+        <v>12128</v>
       </c>
       <c r="B109">
-        <v>332</v>
+        <v>1</v>
       </c>
       <c r="C109">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>9789</v>
+        <v>12304</v>
       </c>
       <c r="B110">
         <v>1</v>
       </c>
       <c r="C110">
-        <v>7</v>
+        <v>67</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>9833</v>
+        <v>12539</v>
       </c>
       <c r="B111">
         <v>2</v>
       </c>
       <c r="C111">
-        <v>74</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>9910</v>
+        <v>12543</v>
       </c>
       <c r="B112">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C112">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>10105</v>
+        <v>12607</v>
       </c>
       <c r="B113">
         <v>3</v>
@@ -1628,398 +1628,332 @@
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>10529</v>
+        <v>12608</v>
       </c>
       <c r="B114">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C114">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>10993</v>
+        <v>12675</v>
       </c>
       <c r="B115">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C115">
-        <v>32</v>
+        <v>118</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11114</v>
+        <v>12676</v>
       </c>
       <c r="B116">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C116">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>11131</v>
+        <v>12677</v>
       </c>
       <c r="B117">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C117">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>11134</v>
+        <v>12870</v>
       </c>
       <c r="B118">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C118">
-        <v>8</v>
+        <v>163</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>11150</v>
+        <v>12979</v>
       </c>
       <c r="B119">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C119">
-        <v>26</v>
+        <v>372</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>11357</v>
+        <v>13034</v>
       </c>
       <c r="B120">
         <v>3</v>
       </c>
       <c r="C120">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>11396</v>
+        <v>14017</v>
       </c>
       <c r="B121">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C121">
-        <v>51</v>
+        <v>114</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>11555</v>
+        <v>19583</v>
       </c>
       <c r="B122">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C122">
-        <v>77</v>
+        <v>470</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>11687</v>
+        <v>19986</v>
       </c>
       <c r="B123">
         <v>2</v>
       </c>
       <c r="C123">
-        <v>186</v>
+        <v>34</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>11689</v>
+        <v>19987</v>
       </c>
       <c r="B124">
         <v>2</v>
       </c>
       <c r="C124">
-        <v>186</v>
+        <v>38</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>11690</v>
+        <v>20486</v>
       </c>
       <c r="B125">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C125">
-        <v>186</v>
+        <v>362</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>11794</v>
+        <v>20498</v>
       </c>
       <c r="B126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C126">
-        <v>94</v>
+        <v>114</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>12128</v>
+        <v>21082</v>
       </c>
       <c r="B127">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C127">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>12539</v>
+        <v>21454</v>
       </c>
       <c r="B128">
         <v>2</v>
       </c>
       <c r="C128">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>12607</v>
+        <v>22049</v>
       </c>
       <c r="B129">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C129">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>12608</v>
+        <v>22089</v>
       </c>
       <c r="B130">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C130">
-        <v>7</v>
+        <v>121</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>12675</v>
+        <v>22313</v>
       </c>
       <c r="B131">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C131">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>12676</v>
+        <v>23234</v>
       </c>
       <c r="B132">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C132">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>12677</v>
+        <v>23235</v>
       </c>
       <c r="B133">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C133">
-        <v>7</v>
+        <v>95</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>12870</v>
+        <v>24127</v>
       </c>
       <c r="B134">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C134">
-        <v>136</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>12923</v>
+        <v>24252</v>
       </c>
       <c r="B135">
         <v>1</v>
       </c>
       <c r="C135">
-        <v>35</v>
+        <v>110</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>12925</v>
+        <v>24257</v>
       </c>
       <c r="B136">
         <v>1</v>
       </c>
       <c r="C136">
-        <v>37</v>
+        <v>83</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>13259</v>
+        <v>24260</v>
       </c>
       <c r="B137">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C137">
-        <v>34</v>
+        <v>82</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>13962</v>
+        <v>24566</v>
       </c>
       <c r="B138">
         <v>1</v>
       </c>
       <c r="C138">
-        <v>58</v>
+        <v>353</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>20650</v>
+        <v>24567</v>
       </c>
       <c r="B139">
         <v>1</v>
       </c>
       <c r="C139">
-        <v>7</v>
+        <v>360</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>21082</v>
+        <v>24844</v>
       </c>
       <c r="B140">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C140">
-        <v>15</v>
+        <v>108</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>21793</v>
+        <v>25278</v>
       </c>
       <c r="B141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C141">
-        <v>414</v>
+        <v>329</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>22089</v>
+        <v>25286</v>
       </c>
       <c r="B142">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C142">
-        <v>10</v>
+        <v>46</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>22317</v>
+        <v>26103</v>
       </c>
       <c r="B143">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C143">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3">
-      <c r="A144">
-        <v>23235</v>
-      </c>
-      <c r="B144">
-        <v>25</v>
-      </c>
-      <c r="C144">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3">
-      <c r="A145">
-        <v>23992</v>
-      </c>
-      <c r="B145">
-        <v>29</v>
-      </c>
-      <c r="C145">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3">
-      <c r="A146">
-        <v>24252</v>
-      </c>
-      <c r="B146">
-        <v>1</v>
-      </c>
-      <c r="C146">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3">
-      <c r="A147">
-        <v>24257</v>
-      </c>
-      <c r="B147">
-        <v>1</v>
-      </c>
-      <c r="C147">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3">
-      <c r="A148">
-        <v>24258</v>
-      </c>
-      <c r="B148">
-        <v>1</v>
-      </c>
-      <c r="C148">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3">
-      <c r="A149">
-        <v>24260</v>
-      </c>
-      <c r="B149">
-        <v>1</v>
-      </c>
-      <c r="C149">
-        <v>83</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_700.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_700.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C143"/>
+  <dimension ref="A1:C145"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,7 +396,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -407,409 +407,409 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3">
-        <v>67</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>89</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5">
-        <v>132</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>40</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C8">
-        <v>27</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>123</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>155</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11">
-        <v>90</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12">
-        <v>90</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>152</v>
+        <v>97</v>
       </c>
       <c r="B13">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C13">
-        <v>72</v>
+        <v>611</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>159</v>
+        <v>105</v>
       </c>
       <c r="B14">
         <v>3</v>
       </c>
       <c r="C14">
-        <v>439</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>167</v>
+        <v>107</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>132</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>168</v>
+        <v>110</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16">
-        <v>310</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>307</v>
+        <v>130</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>174</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>308</v>
+        <v>143</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>336</v>
+        <v>144</v>
       </c>
       <c r="B19">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>65</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>410</v>
+        <v>146</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20">
-        <v>62</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>414</v>
+        <v>151</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21">
-        <v>101</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>475</v>
+        <v>159</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C22">
-        <v>30</v>
+        <v>877</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>515</v>
+        <v>161</v>
       </c>
       <c r="B23">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C23">
-        <v>119</v>
+        <v>573</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>524</v>
+        <v>167</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C24">
-        <v>48</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>590</v>
+        <v>305</v>
       </c>
       <c r="B25">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C25">
-        <v>57</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>641</v>
+        <v>336</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C26">
-        <v>7</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>903</v>
+        <v>416</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27">
-        <v>87</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>924</v>
+        <v>470</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>926</v>
+        <v>475</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>972</v>
+        <v>590</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C30">
-        <v>353</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>974</v>
+        <v>615</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C31">
-        <v>89</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1082</v>
+        <v>903</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1124</v>
+        <v>922</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33">
-        <v>109</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1243</v>
+        <v>926</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34">
-        <v>56</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1309</v>
+        <v>947</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C35">
-        <v>381</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1447</v>
+        <v>951</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C36">
-        <v>23</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1598</v>
+        <v>1163</v>
       </c>
       <c r="B37">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>205</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1602</v>
+        <v>1414</v>
       </c>
       <c r="B38">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="C38">
-        <v>94</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>1880</v>
+        <v>1490</v>
       </c>
       <c r="B39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C39">
-        <v>132</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -825,120 +825,120 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2109</v>
+        <v>2054</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C41">
-        <v>22</v>
+        <v>277</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2188</v>
+        <v>2055</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C42">
-        <v>485</v>
+        <v>279</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2322</v>
+        <v>2057</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43">
-        <v>66</v>
+        <v>277</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2326</v>
+        <v>2109</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44">
-        <v>60</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2331</v>
+        <v>2188</v>
       </c>
       <c r="B45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45">
-        <v>73</v>
+        <v>475</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2419</v>
+        <v>2335</v>
       </c>
       <c r="B46">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C46">
-        <v>21</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="B47">
         <v>80</v>
       </c>
       <c r="C47">
-        <v>145</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="B48">
         <v>80</v>
       </c>
       <c r="C48">
-        <v>135</v>
+        <v>218</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2438</v>
+        <v>2424</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C49">
-        <v>744</v>
+        <v>133</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>3016</v>
+        <v>2438</v>
       </c>
       <c r="B50">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C50">
-        <v>30</v>
+        <v>372</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>3454</v>
+        <v>2497</v>
       </c>
       <c r="B51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51">
         <v>7</v>
@@ -946,120 +946,120 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>3477</v>
+        <v>2859</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C52">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>3577</v>
+        <v>2912</v>
       </c>
       <c r="B53">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C53">
-        <v>118</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>3673</v>
+        <v>2991</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C54">
-        <v>144</v>
+        <v>89</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3982</v>
+        <v>3048</v>
       </c>
       <c r="B55">
         <v>3</v>
       </c>
       <c r="C55">
-        <v>459</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>4955</v>
+        <v>3429</v>
       </c>
       <c r="B56">
-        <v>332</v>
+        <v>15</v>
       </c>
       <c r="C56">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>4957</v>
+        <v>3430</v>
       </c>
       <c r="B57">
-        <v>332</v>
+        <v>15</v>
       </c>
       <c r="C57">
-        <v>16</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>4960</v>
+        <v>3434</v>
       </c>
       <c r="B58">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C58">
-        <v>26</v>
+        <v>53</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>5081</v>
+        <v>3454</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C59">
-        <v>108</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>5152</v>
+        <v>3478</v>
       </c>
       <c r="B60">
         <v>2</v>
       </c>
       <c r="C60">
-        <v>14</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>5243</v>
+        <v>3577</v>
       </c>
       <c r="B61">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C61">
-        <v>146</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>5341</v>
+        <v>3670</v>
       </c>
       <c r="B62">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C62">
         <v>7</v>
@@ -1067,384 +1067,384 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>5647</v>
+        <v>5005</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C63">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>5652</v>
+        <v>5083</v>
       </c>
       <c r="B64">
         <v>2</v>
       </c>
       <c r="C64">
-        <v>32</v>
+        <v>73</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5654</v>
+        <v>5097</v>
       </c>
       <c r="B65">
         <v>2</v>
       </c>
       <c r="C65">
-        <v>7</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5733</v>
+        <v>5165</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C66">
-        <v>58</v>
+        <v>28</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5966</v>
+        <v>5208</v>
       </c>
       <c r="B67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C67">
-        <v>7</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5967</v>
+        <v>5493</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C68">
-        <v>7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>6097</v>
+        <v>5584</v>
       </c>
       <c r="B69">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C69">
-        <v>81</v>
+        <v>153</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>6098</v>
+        <v>5585</v>
       </c>
       <c r="B70">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C70">
-        <v>44</v>
+        <v>157</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>6158</v>
+        <v>5647</v>
       </c>
       <c r="B71">
         <v>2</v>
       </c>
       <c r="C71">
-        <v>305</v>
+        <v>49</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>6575</v>
+        <v>5813</v>
       </c>
       <c r="B72">
         <v>3</v>
       </c>
       <c r="C72">
-        <v>314</v>
+        <v>677</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>7885</v>
+        <v>5966</v>
       </c>
       <c r="B73">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C73">
-        <v>82</v>
+        <v>18</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>7886</v>
+        <v>5967</v>
       </c>
       <c r="B74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C74">
-        <v>84</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>8104</v>
+        <v>6097</v>
       </c>
       <c r="B75">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C75">
-        <v>119</v>
+        <v>40</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>8217</v>
+        <v>6098</v>
       </c>
       <c r="B76">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="C76">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>8283</v>
+        <v>7084</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C77">
-        <v>295</v>
+        <v>149</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>8284</v>
+        <v>7558</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C78">
-        <v>295</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>8286</v>
+        <v>7707</v>
       </c>
       <c r="B79">
         <v>2</v>
       </c>
       <c r="C79">
-        <v>295</v>
+        <v>197</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>8635</v>
+        <v>7886</v>
       </c>
       <c r="B80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C80">
-        <v>205</v>
+        <v>84</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>8753</v>
+        <v>8104</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81">
-        <v>212</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>8943</v>
+        <v>8283</v>
       </c>
       <c r="B82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C82">
-        <v>225</v>
+        <v>295</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>9577</v>
+        <v>8284</v>
       </c>
       <c r="B83">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C83">
-        <v>20</v>
+        <v>295</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>9789</v>
+        <v>8285</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84">
-        <v>7</v>
+        <v>295</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>10105</v>
+        <v>8286</v>
       </c>
       <c r="B85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C85">
-        <v>7</v>
+        <v>295</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>10149</v>
+        <v>8635</v>
       </c>
       <c r="B86">
         <v>3</v>
       </c>
       <c r="C86">
-        <v>736</v>
+        <v>204</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>10465</v>
+        <v>8649</v>
       </c>
       <c r="B87">
         <v>2</v>
       </c>
       <c r="C87">
-        <v>7</v>
+        <v>216</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>10529</v>
+        <v>8650</v>
       </c>
       <c r="B88">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C88">
-        <v>32</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>10716</v>
+        <v>8677</v>
       </c>
       <c r="B89">
         <v>3</v>
       </c>
       <c r="C89">
-        <v>57</v>
+        <v>343</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>10780</v>
+        <v>8754</v>
       </c>
       <c r="B90">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C90">
-        <v>7</v>
+        <v>211</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>10825</v>
+        <v>8926</v>
       </c>
       <c r="B91">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C91">
-        <v>400</v>
+        <v>68</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>11081</v>
+        <v>9065</v>
       </c>
       <c r="B92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C92">
-        <v>216</v>
+        <v>186</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>11093</v>
+        <v>9068</v>
       </c>
       <c r="B93">
         <v>1</v>
       </c>
       <c r="C93">
-        <v>61</v>
+        <v>74</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>11116</v>
+        <v>9085</v>
       </c>
       <c r="B94">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C94">
-        <v>46</v>
+        <v>25</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>11134</v>
+        <v>9289</v>
       </c>
       <c r="B95">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C95">
-        <v>8</v>
+        <v>75</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>11150</v>
+        <v>9507</v>
       </c>
       <c r="B96">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C96">
-        <v>26</v>
+        <v>119</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>11357</v>
+        <v>9577</v>
       </c>
       <c r="B97">
-        <v>3</v>
+        <v>332</v>
       </c>
       <c r="C97">
         <v>7</v>
@@ -1452,508 +1452,530 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>11404</v>
+        <v>9789</v>
       </c>
       <c r="B98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98">
-        <v>67</v>
+        <v>11</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>11492</v>
+        <v>9829</v>
       </c>
       <c r="B99">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C99">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>11493</v>
+        <v>9910</v>
       </c>
       <c r="B100">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C100">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>11555</v>
+        <v>10105</v>
       </c>
       <c r="B101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C101">
-        <v>76</v>
+        <v>41</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>11687</v>
+        <v>10529</v>
       </c>
       <c r="B102">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C102">
-        <v>186</v>
+        <v>24</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>11885</v>
+        <v>10530</v>
       </c>
       <c r="B103">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C103">
-        <v>227</v>
+        <v>22</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>11886</v>
+        <v>11116</v>
       </c>
       <c r="B104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C104">
-        <v>114</v>
+        <v>47</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>11914</v>
+        <v>11134</v>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C105">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11967</v>
+        <v>11150</v>
       </c>
       <c r="B106">
         <v>1</v>
       </c>
       <c r="C106">
-        <v>79</v>
+        <v>26</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11969</v>
+        <v>11357</v>
       </c>
       <c r="B107">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C107">
-        <v>44</v>
+        <v>55</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11971</v>
+        <v>11492</v>
       </c>
       <c r="B108">
         <v>1</v>
       </c>
       <c r="C108">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>12128</v>
+        <v>11493</v>
       </c>
       <c r="B109">
         <v>1</v>
       </c>
       <c r="C109">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>12304</v>
+        <v>11681</v>
       </c>
       <c r="B110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C110">
-        <v>67</v>
+        <v>13</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>12539</v>
+        <v>11687</v>
       </c>
       <c r="B111">
         <v>2</v>
       </c>
       <c r="C111">
-        <v>7</v>
+        <v>186</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>12543</v>
+        <v>11690</v>
       </c>
       <c r="B112">
         <v>2</v>
       </c>
       <c r="C112">
-        <v>7</v>
+        <v>186</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>12607</v>
+        <v>11794</v>
       </c>
       <c r="B113">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C113">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>12608</v>
+        <v>11886</v>
       </c>
       <c r="B114">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C114">
-        <v>7</v>
+        <v>113</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>12675</v>
+        <v>11914</v>
       </c>
       <c r="B115">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C115">
-        <v>118</v>
+        <v>47</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>12676</v>
+        <v>11952</v>
       </c>
       <c r="B116">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C116">
-        <v>7</v>
+        <v>319</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>12677</v>
+        <v>11967</v>
       </c>
       <c r="B117">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C117">
-        <v>7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>12870</v>
+        <v>12304</v>
       </c>
       <c r="B118">
         <v>1</v>
       </c>
       <c r="C118">
-        <v>163</v>
+        <v>67</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12979</v>
+        <v>12608</v>
       </c>
       <c r="B119">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C119">
-        <v>372</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>13034</v>
+        <v>12675</v>
       </c>
       <c r="B120">
         <v>3</v>
       </c>
       <c r="C120">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>14017</v>
+        <v>12676</v>
       </c>
       <c r="B121">
         <v>3</v>
       </c>
       <c r="C121">
-        <v>114</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>19583</v>
+        <v>12677</v>
       </c>
       <c r="B122">
         <v>3</v>
       </c>
       <c r="C122">
-        <v>470</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>19986</v>
+        <v>12791</v>
       </c>
       <c r="B123">
         <v>2</v>
       </c>
       <c r="C123">
-        <v>34</v>
+        <v>472</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>19987</v>
+        <v>12870</v>
       </c>
       <c r="B124">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C124">
-        <v>38</v>
+        <v>81</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>20486</v>
+        <v>12923</v>
       </c>
       <c r="B125">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C125">
-        <v>362</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>20498</v>
+        <v>12924</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126">
-        <v>114</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>21082</v>
+        <v>13023</v>
       </c>
       <c r="B127">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C127">
-        <v>10</v>
+        <v>342</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>21454</v>
+        <v>13034</v>
       </c>
       <c r="B128">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C128">
-        <v>21</v>
+        <v>342</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>22049</v>
+        <v>13249</v>
       </c>
       <c r="B129">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C129">
-        <v>10</v>
+        <v>76</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>22089</v>
+        <v>14037</v>
       </c>
       <c r="B130">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C130">
-        <v>121</v>
+        <v>201</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>22313</v>
+        <v>19924</v>
       </c>
       <c r="B131">
         <v>2</v>
       </c>
       <c r="C131">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>23234</v>
+        <v>19981</v>
       </c>
       <c r="B132">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C132">
-        <v>55</v>
+        <v>37</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>23235</v>
+        <v>19986</v>
       </c>
       <c r="B133">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C133">
-        <v>95</v>
+        <v>44</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>24127</v>
+        <v>20208</v>
       </c>
       <c r="B134">
         <v>3</v>
       </c>
       <c r="C134">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>24252</v>
+        <v>21082</v>
       </c>
       <c r="B135">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C135">
-        <v>110</v>
+        <v>220</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>24257</v>
+        <v>21454</v>
       </c>
       <c r="B136">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C136">
-        <v>83</v>
+        <v>21</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>24260</v>
+        <v>22089</v>
       </c>
       <c r="B137">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C137">
-        <v>82</v>
+        <v>10</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>24566</v>
+        <v>22313</v>
       </c>
       <c r="B138">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C138">
-        <v>353</v>
+        <v>40</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>24567</v>
+        <v>22554</v>
       </c>
       <c r="B139">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C139">
-        <v>360</v>
+        <v>427</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>24844</v>
+        <v>23235</v>
       </c>
       <c r="B140">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C140">
-        <v>108</v>
+        <v>49</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>25278</v>
+        <v>23992</v>
       </c>
       <c r="B141">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C141">
-        <v>329</v>
+        <v>24</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>25286</v>
+        <v>24257</v>
       </c>
       <c r="B142">
         <v>1</v>
       </c>
       <c r="C142">
-        <v>46</v>
+        <v>164</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
+        <v>24707</v>
+      </c>
+      <c r="B143">
+        <v>3</v>
+      </c>
+      <c r="C143">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144">
+        <v>25286</v>
+      </c>
+      <c r="B144">
+        <v>1</v>
+      </c>
+      <c r="C144">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145">
         <v>26103</v>
       </c>
-      <c r="B143">
-        <v>2</v>
-      </c>
-      <c r="C143">
-        <v>26</v>
+      <c r="B145">
+        <v>2</v>
+      </c>
+      <c r="C145">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_700.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_700.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C145"/>
+  <dimension ref="A1:C146"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,593 +396,593 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>67</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>87</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C4">
-        <v>66</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>67</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6">
-        <v>66</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>246</v>
+        <v>329</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="B8">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>45</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>156</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C10">
-        <v>71</v>
+        <v>977</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>31</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="B13">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C13">
-        <v>611</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B14">
         <v>3</v>
       </c>
       <c r="C14">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>110</v>
+        <v>159</v>
       </c>
       <c r="B16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16">
-        <v>125</v>
+        <v>441</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>430</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18">
-        <v>90</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>144</v>
+        <v>206</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19">
-        <v>90</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>146</v>
+        <v>305</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>151</v>
+        <v>336</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C21">
-        <v>7</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>159</v>
+        <v>345</v>
       </c>
       <c r="B22">
         <v>3</v>
       </c>
       <c r="C22">
-        <v>877</v>
+        <v>373</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>161</v>
+        <v>346</v>
       </c>
       <c r="B23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>573</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>167</v>
+        <v>415</v>
       </c>
       <c r="B24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>131</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>305</v>
+        <v>434</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25">
-        <v>87</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>336</v>
+        <v>435</v>
       </c>
       <c r="B26">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C26">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>416</v>
+        <v>590</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C27">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>470</v>
+        <v>926</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>475</v>
+        <v>944</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C29">
-        <v>41</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>590</v>
+        <v>947</v>
       </c>
       <c r="B30">
         <v>15</v>
       </c>
       <c r="C30">
-        <v>57</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>615</v>
+        <v>972</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C31">
-        <v>58</v>
+        <v>352</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>903</v>
+        <v>1070</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>670</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>922</v>
+        <v>1080</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C33">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>926</v>
+        <v>1309</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34">
-        <v>24</v>
+        <v>386</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>947</v>
+        <v>1413</v>
       </c>
       <c r="B35">
         <v>15</v>
       </c>
       <c r="C35">
-        <v>24</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>951</v>
+        <v>1429</v>
       </c>
       <c r="B36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C36">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1163</v>
+        <v>1490</v>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C37">
-        <v>205</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1414</v>
+        <v>1504</v>
       </c>
       <c r="B38">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C38">
-        <v>59</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>1490</v>
+        <v>1598</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C39">
-        <v>55</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2049</v>
+        <v>1622</v>
       </c>
       <c r="B40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C40">
-        <v>323</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2054</v>
+        <v>2049</v>
       </c>
       <c r="B41">
         <v>3</v>
       </c>
       <c r="C41">
-        <v>277</v>
+        <v>426</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2055</v>
+        <v>2057</v>
       </c>
       <c r="B42">
         <v>3</v>
       </c>
       <c r="C42">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2057</v>
+        <v>2188</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C43">
-        <v>277</v>
+        <v>471</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2109</v>
+        <v>2326</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2188</v>
+        <v>2328</v>
       </c>
       <c r="B45">
         <v>2</v>
       </c>
       <c r="C45">
-        <v>475</v>
+        <v>185</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2335</v>
+        <v>2419</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C46">
-        <v>120</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="B47">
         <v>80</v>
       </c>
       <c r="C47">
-        <v>109</v>
+        <v>218</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="B48">
         <v>80</v>
       </c>
       <c r="C48">
-        <v>218</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2424</v>
+        <v>2438</v>
       </c>
       <c r="B49">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C49">
-        <v>133</v>
+        <v>743</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2438</v>
+        <v>2537</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>372</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2497</v>
+        <v>2538</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2859</v>
+        <v>2539</v>
       </c>
       <c r="B52">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C52">
-        <v>42</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>2912</v>
+        <v>2726</v>
       </c>
       <c r="B53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C53">
-        <v>28</v>
+        <v>141</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>2991</v>
+        <v>2735</v>
       </c>
       <c r="B54">
         <v>3</v>
       </c>
       <c r="C54">
-        <v>89</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3048</v>
+        <v>2775</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C55">
         <v>7</v>
@@ -990,673 +990,673 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3429</v>
+        <v>2859</v>
       </c>
       <c r="B56">
         <v>15</v>
       </c>
       <c r="C56">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3430</v>
+        <v>2879</v>
       </c>
       <c r="B57">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C57">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3434</v>
+        <v>2912</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C58">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3454</v>
+        <v>2991</v>
       </c>
       <c r="B59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C59">
-        <v>7</v>
+        <v>178</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3478</v>
+        <v>3016</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C60">
-        <v>44</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>3577</v>
+        <v>3257</v>
       </c>
       <c r="B61">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C61">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3670</v>
+        <v>3258</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>5005</v>
+        <v>3429</v>
       </c>
       <c r="B63">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C63">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>5083</v>
+        <v>3430</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C64">
-        <v>73</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5097</v>
+        <v>3454</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65">
-        <v>179</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5165</v>
+        <v>3477</v>
       </c>
       <c r="B66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C66">
-        <v>28</v>
+        <v>61</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5208</v>
+        <v>3576</v>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C67">
-        <v>330</v>
+        <v>59</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5493</v>
+        <v>3900</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C68">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5584</v>
+        <v>3961</v>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C69">
-        <v>153</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5585</v>
+        <v>3980</v>
       </c>
       <c r="B70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C70">
-        <v>157</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5647</v>
+        <v>3982</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C71">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5813</v>
+        <v>4076</v>
       </c>
       <c r="B72">
         <v>3</v>
       </c>
       <c r="C72">
-        <v>677</v>
+        <v>228</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5966</v>
+        <v>4246</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73">
-        <v>18</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5967</v>
+        <v>5083</v>
       </c>
       <c r="B74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C74">
-        <v>10</v>
+        <v>73</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>6097</v>
+        <v>5097</v>
       </c>
       <c r="B75">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C75">
-        <v>40</v>
+        <v>88</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>6098</v>
+        <v>5151</v>
       </c>
       <c r="B76">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C76">
-        <v>59</v>
+        <v>14</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>7084</v>
+        <v>5165</v>
       </c>
       <c r="B77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>149</v>
+        <v>28</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>7558</v>
+        <v>5208</v>
       </c>
       <c r="B78">
         <v>3</v>
       </c>
       <c r="C78">
-        <v>50</v>
+        <v>330</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>7707</v>
+        <v>5647</v>
       </c>
       <c r="B79">
         <v>2</v>
       </c>
       <c r="C79">
-        <v>197</v>
+        <v>38</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>7886</v>
+        <v>5649</v>
       </c>
       <c r="B80">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C80">
-        <v>84</v>
+        <v>38</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>8104</v>
+        <v>5744</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>8283</v>
+        <v>5966</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C82">
-        <v>295</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>8284</v>
+        <v>5967</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C83">
-        <v>295</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>8285</v>
+        <v>6097</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C84">
-        <v>295</v>
+        <v>40</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>8286</v>
+        <v>6098</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C85">
-        <v>295</v>
+        <v>44</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>8635</v>
+        <v>6936</v>
       </c>
       <c r="B86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C86">
-        <v>204</v>
+        <v>312</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>8649</v>
+        <v>7084</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C87">
-        <v>216</v>
+        <v>149</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>8650</v>
+        <v>7704</v>
       </c>
       <c r="B88">
         <v>2</v>
       </c>
       <c r="C88">
-        <v>214</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>8677</v>
+        <v>7707</v>
       </c>
       <c r="B89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C89">
-        <v>343</v>
+        <v>201</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>8754</v>
+        <v>7885</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C90">
-        <v>211</v>
+        <v>82</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>8926</v>
+        <v>7886</v>
       </c>
       <c r="B91">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C91">
-        <v>68</v>
+        <v>84</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>9065</v>
+        <v>8120</v>
       </c>
       <c r="B92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C92">
-        <v>186</v>
+        <v>316</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>9068</v>
+        <v>8121</v>
       </c>
       <c r="B93">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C93">
-        <v>74</v>
+        <v>172</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>9085</v>
+        <v>8283</v>
       </c>
       <c r="B94">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C94">
-        <v>25</v>
+        <v>277</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>9289</v>
+        <v>8284</v>
       </c>
       <c r="B95">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C95">
-        <v>75</v>
+        <v>282</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>9507</v>
+        <v>8286</v>
       </c>
       <c r="B96">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C96">
-        <v>119</v>
+        <v>278</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>9577</v>
+        <v>8853</v>
       </c>
       <c r="B97">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C97">
-        <v>7</v>
+        <v>315</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>9789</v>
+        <v>8943</v>
       </c>
       <c r="B98">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C98">
-        <v>11</v>
+        <v>433</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>9829</v>
+        <v>9507</v>
       </c>
       <c r="B99">
         <v>3</v>
       </c>
       <c r="C99">
-        <v>55</v>
+        <v>121</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>9910</v>
+        <v>9577</v>
       </c>
       <c r="B100">
-        <v>25</v>
+        <v>332</v>
       </c>
       <c r="C100">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>10105</v>
+        <v>9789</v>
       </c>
       <c r="B101">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C101">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>10529</v>
+        <v>9829</v>
       </c>
       <c r="B102">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C102">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>10530</v>
+        <v>10105</v>
       </c>
       <c r="B103">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C103">
-        <v>22</v>
+        <v>83</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>11116</v>
+        <v>10149</v>
       </c>
       <c r="B104">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C104">
-        <v>47</v>
+        <v>556</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>11134</v>
+        <v>10172</v>
       </c>
       <c r="B105">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C105">
-        <v>7</v>
+        <v>724</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11150</v>
+        <v>10641</v>
       </c>
       <c r="B106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C106">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11357</v>
+        <v>10780</v>
       </c>
       <c r="B107">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C107">
-        <v>55</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11492</v>
+        <v>10825</v>
       </c>
       <c r="B108">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C108">
-        <v>55</v>
+        <v>13</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11493</v>
+        <v>11081</v>
       </c>
       <c r="B109">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C109">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11681</v>
+        <v>11093</v>
       </c>
       <c r="B110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C110">
-        <v>13</v>
+        <v>46</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11687</v>
+        <v>11134</v>
       </c>
       <c r="B111">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C111">
-        <v>186</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11690</v>
+        <v>11357</v>
       </c>
       <c r="B112">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C112">
-        <v>186</v>
+        <v>55</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11794</v>
+        <v>11492</v>
       </c>
       <c r="B113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C113">
-        <v>59</v>
+        <v>18</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11886</v>
+        <v>11493</v>
       </c>
       <c r="B114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C114">
-        <v>113</v>
+        <v>26</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11914</v>
+        <v>11510</v>
       </c>
       <c r="B115">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C115">
-        <v>47</v>
+        <v>352</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11952</v>
+        <v>11886</v>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C116">
-        <v>319</v>
+        <v>222</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -1667,26 +1667,26 @@
         <v>1</v>
       </c>
       <c r="C117">
-        <v>80</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>12304</v>
+        <v>11969</v>
       </c>
       <c r="B118">
         <v>1</v>
       </c>
       <c r="C118">
-        <v>67</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12608</v>
+        <v>12304</v>
       </c>
       <c r="B119">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C119">
         <v>7</v>
@@ -1694,7 +1694,7 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12675</v>
+        <v>12608</v>
       </c>
       <c r="B120">
         <v>3</v>
@@ -1705,21 +1705,21 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12676</v>
+        <v>12661</v>
       </c>
       <c r="B121">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C121">
-        <v>7</v>
+        <v>87</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12677</v>
+        <v>12662</v>
       </c>
       <c r="B122">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C122">
         <v>7</v>
@@ -1727,32 +1727,32 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12791</v>
+        <v>12675</v>
       </c>
       <c r="B123">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C123">
-        <v>472</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12870</v>
+        <v>12676</v>
       </c>
       <c r="B124">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C124">
-        <v>81</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12923</v>
+        <v>12677</v>
       </c>
       <c r="B125">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C125">
         <v>7</v>
@@ -1760,13 +1760,13 @@
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12924</v>
+        <v>12791</v>
       </c>
       <c r="B126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C126">
-        <v>7</v>
+        <v>468</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -1788,100 +1788,100 @@
         <v>3</v>
       </c>
       <c r="C128">
-        <v>342</v>
+        <v>684</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>13249</v>
+        <v>13263</v>
       </c>
       <c r="B129">
         <v>29</v>
       </c>
       <c r="C129">
-        <v>76</v>
+        <v>40</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>14037</v>
+        <v>19986</v>
       </c>
       <c r="B130">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C130">
-        <v>201</v>
+        <v>45</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>19924</v>
+        <v>20208</v>
       </c>
       <c r="B131">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C131">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>19981</v>
+        <v>20486</v>
       </c>
       <c r="B132">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C132">
-        <v>37</v>
+        <v>354</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>19986</v>
+        <v>21082</v>
       </c>
       <c r="B133">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C133">
-        <v>44</v>
+        <v>227</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>20208</v>
+        <v>21091</v>
       </c>
       <c r="B134">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C134">
-        <v>22</v>
+        <v>74</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>21082</v>
+        <v>21454</v>
       </c>
       <c r="B135">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C135">
-        <v>220</v>
+        <v>21</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>21454</v>
+        <v>21793</v>
       </c>
       <c r="B136">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C136">
-        <v>21</v>
+        <v>374</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>22089</v>
+        <v>22049</v>
       </c>
       <c r="B137">
         <v>10</v>
@@ -1892,13 +1892,13 @@
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>22313</v>
+        <v>22089</v>
       </c>
       <c r="B138">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C138">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -1909,40 +1909,40 @@
         <v>10</v>
       </c>
       <c r="C139">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>23235</v>
+        <v>23611</v>
       </c>
       <c r="B140">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C140">
-        <v>49</v>
+        <v>394</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>23992</v>
+        <v>24252</v>
       </c>
       <c r="B141">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C141">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>24257</v>
+        <v>24260</v>
       </c>
       <c r="B142">
         <v>1</v>
       </c>
       <c r="C142">
-        <v>164</v>
+        <v>109</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -1953,29 +1953,40 @@
         <v>3</v>
       </c>
       <c r="C143">
-        <v>720</v>
+        <v>717</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>25286</v>
+        <v>25278</v>
       </c>
       <c r="B144">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C144">
-        <v>47</v>
+        <v>164</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
+        <v>25286</v>
+      </c>
+      <c r="B145">
+        <v>1</v>
+      </c>
+      <c r="C145">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146">
         <v>26103</v>
       </c>
-      <c r="B145">
-        <v>2</v>
-      </c>
-      <c r="C145">
-        <v>52</v>
+      <c r="B146">
+        <v>2</v>
+      </c>
+      <c r="C146">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_700.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_700.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C146"/>
+  <dimension ref="A1:C148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,277 +396,277 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>127</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>400</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="B4">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>7</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B5">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>132</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6">
-        <v>117</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>329</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C8">
-        <v>70</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C9">
-        <v>1290</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="B10">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>977</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>153</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C12">
-        <v>28</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13">
-        <v>125</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>154</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C15">
-        <v>34</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>441</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B17">
         <v>3</v>
       </c>
       <c r="C17">
-        <v>430</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B18">
         <v>3</v>
       </c>
       <c r="C18">
-        <v>234</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19">
-        <v>62</v>
+        <v>370</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>305</v>
+        <v>205</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>336</v>
+        <v>206</v>
       </c>
       <c r="B21">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>345</v>
+        <v>308</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C22">
-        <v>373</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C23">
-        <v>176</v>
+        <v>370</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>415</v>
+        <v>346</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24">
-        <v>96</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>434</v>
+        <v>411</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>435</v>
+        <v>413</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -682,68 +682,68 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>926</v>
+        <v>641</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>944</v>
+        <v>903</v>
       </c>
       <c r="B29">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>947</v>
+        <v>926</v>
       </c>
       <c r="B30">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>972</v>
+        <v>944</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C31">
-        <v>352</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1070</v>
+        <v>1080</v>
       </c>
       <c r="B32">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C32">
-        <v>670</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="B33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C33">
-        <v>107</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -754,51 +754,51 @@
         <v>2</v>
       </c>
       <c r="C34">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1413</v>
+        <v>1406</v>
       </c>
       <c r="B35">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C35">
-        <v>119</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1429</v>
+        <v>1413</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1490</v>
+        <v>1414</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C37">
-        <v>92</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1504</v>
+        <v>1490</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>100</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -814,24 +814,24 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>1622</v>
+        <v>2050</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C40">
-        <v>120</v>
+        <v>277</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2049</v>
+        <v>2054</v>
       </c>
       <c r="B41">
         <v>3</v>
       </c>
       <c r="C41">
-        <v>426</v>
+        <v>273</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -847,450 +847,450 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2188</v>
+        <v>2103</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C43">
-        <v>471</v>
+        <v>387</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2326</v>
+        <v>2424</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C44">
-        <v>7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2328</v>
+        <v>2537</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C45">
-        <v>185</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2419</v>
+        <v>2538</v>
       </c>
       <c r="B46">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2423</v>
+        <v>2539</v>
       </c>
       <c r="B47">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="C47">
-        <v>218</v>
+        <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2424</v>
+        <v>2726</v>
       </c>
       <c r="B48">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C48">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2438</v>
+        <v>2728</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C49">
-        <v>743</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2537</v>
+        <v>2859</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C50">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2538</v>
+        <v>2916</v>
       </c>
       <c r="B51">
         <v>1</v>
       </c>
       <c r="C51">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2539</v>
+        <v>2991</v>
       </c>
       <c r="B52">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C52">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>2726</v>
+        <v>3016</v>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C53">
-        <v>141</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>2735</v>
+        <v>3021</v>
       </c>
       <c r="B54">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C54">
-        <v>59</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>2775</v>
+        <v>3079</v>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C55">
-        <v>7</v>
+        <v>90</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>2859</v>
+        <v>3257</v>
       </c>
       <c r="B56">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C56">
-        <v>42</v>
+        <v>62</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>2879</v>
+        <v>3258</v>
       </c>
       <c r="B57">
         <v>1</v>
       </c>
       <c r="C57">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>2912</v>
+        <v>3430</v>
       </c>
       <c r="B58">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C58">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>2991</v>
+        <v>3454</v>
       </c>
       <c r="B59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C59">
-        <v>178</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3016</v>
+        <v>3477</v>
       </c>
       <c r="B60">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C60">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>3257</v>
+        <v>3576</v>
       </c>
       <c r="B61">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C61">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3258</v>
+        <v>3577</v>
       </c>
       <c r="B62">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C62">
-        <v>23</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>3429</v>
+        <v>3955</v>
       </c>
       <c r="B63">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C63">
-        <v>32</v>
+        <v>66</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>3430</v>
+        <v>3961</v>
       </c>
       <c r="B64">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C64">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>3454</v>
+        <v>4019</v>
       </c>
       <c r="B65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C65">
-        <v>7</v>
+        <v>104</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>3477</v>
+        <v>4076</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C66">
-        <v>61</v>
+        <v>154</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>3576</v>
+        <v>4246</v>
       </c>
       <c r="B67">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>3900</v>
+        <v>4961</v>
       </c>
       <c r="B68">
-        <v>3</v>
+        <v>332</v>
       </c>
       <c r="C68">
-        <v>63</v>
+        <v>26</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>3961</v>
+        <v>5005</v>
       </c>
       <c r="B69">
         <v>1</v>
       </c>
       <c r="C69">
-        <v>54</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>3980</v>
+        <v>5080</v>
       </c>
       <c r="B70">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C70">
-        <v>7</v>
+        <v>91</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>3982</v>
+        <v>5097</v>
       </c>
       <c r="B71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C71">
-        <v>17</v>
+        <v>176</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>4076</v>
+        <v>5151</v>
       </c>
       <c r="B72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C72">
-        <v>228</v>
+        <v>14</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>4246</v>
+        <v>5165</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73">
-        <v>100</v>
+        <v>28</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5083</v>
+        <v>5208</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C74">
-        <v>73</v>
+        <v>331</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>5097</v>
+        <v>5243</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C75">
-        <v>88</v>
+        <v>146</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>5151</v>
+        <v>5584</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C76">
-        <v>14</v>
+        <v>276</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>5165</v>
+        <v>5646</v>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C77">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>5208</v>
+        <v>5647</v>
       </c>
       <c r="B78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C78">
-        <v>330</v>
+        <v>38</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>5647</v>
+        <v>5649</v>
       </c>
       <c r="B79">
         <v>2</v>
       </c>
       <c r="C79">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>5649</v>
+        <v>5729</v>
       </c>
       <c r="B80">
         <v>2</v>
       </c>
       <c r="C80">
-        <v>38</v>
+        <v>59</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>5744</v>
+        <v>5812</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C81">
-        <v>28</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>5966</v>
+        <v>5813</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C82">
-        <v>18</v>
+        <v>688</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>5967</v>
+        <v>5831</v>
       </c>
       <c r="B83">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C83">
         <v>7</v>
@@ -1298,208 +1298,208 @@
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>6097</v>
+        <v>5966</v>
       </c>
       <c r="B84">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>6098</v>
+        <v>5967</v>
       </c>
       <c r="B85">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>44</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>6936</v>
+        <v>6097</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C86">
-        <v>312</v>
+        <v>40</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>7084</v>
+        <v>6098</v>
       </c>
       <c r="B87">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C87">
-        <v>149</v>
+        <v>86</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>7704</v>
+        <v>7084</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C88">
-        <v>7</v>
+        <v>149</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>7707</v>
+        <v>7704</v>
       </c>
       <c r="B89">
         <v>2</v>
       </c>
       <c r="C89">
-        <v>201</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>7885</v>
+        <v>8216</v>
       </c>
       <c r="B90">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C90">
-        <v>82</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>7886</v>
+        <v>8217</v>
       </c>
       <c r="B91">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C91">
-        <v>84</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>8120</v>
+        <v>8274</v>
       </c>
       <c r="B92">
         <v>3</v>
       </c>
       <c r="C92">
-        <v>316</v>
+        <v>204</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>8121</v>
+        <v>8284</v>
       </c>
       <c r="B93">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C93">
-        <v>172</v>
+        <v>283</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>8283</v>
+        <v>8557</v>
       </c>
       <c r="B94">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C94">
-        <v>277</v>
+        <v>228</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>8284</v>
+        <v>8898</v>
       </c>
       <c r="B95">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C95">
-        <v>282</v>
+        <v>337</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>8286</v>
+        <v>9082</v>
       </c>
       <c r="B96">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C96">
-        <v>278</v>
+        <v>2911</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>8853</v>
+        <v>9577</v>
       </c>
       <c r="B97">
-        <v>2</v>
+        <v>332</v>
       </c>
       <c r="C97">
-        <v>315</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>8943</v>
+        <v>9608</v>
       </c>
       <c r="B98">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C98">
-        <v>433</v>
+        <v>71</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>9507</v>
+        <v>9613</v>
       </c>
       <c r="B99">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C99">
-        <v>121</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>9577</v>
+        <v>9760</v>
       </c>
       <c r="B100">
-        <v>332</v>
+        <v>29</v>
       </c>
       <c r="C100">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>9789</v>
+        <v>9783</v>
       </c>
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>9829</v>
+        <v>9789</v>
       </c>
       <c r="B102">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C102">
         <v>7</v>
@@ -1507,76 +1507,76 @@
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>10105</v>
+        <v>9997</v>
       </c>
       <c r="B103">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C103">
-        <v>83</v>
+        <v>103</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>10149</v>
+        <v>10105</v>
       </c>
       <c r="B104">
         <v>3</v>
       </c>
       <c r="C104">
-        <v>556</v>
+        <v>83</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>10172</v>
+        <v>10149</v>
       </c>
       <c r="B105">
         <v>3</v>
       </c>
       <c r="C105">
-        <v>724</v>
+        <v>730</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>10641</v>
+        <v>10172</v>
       </c>
       <c r="B106">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C106">
-        <v>7</v>
+        <v>728</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>10780</v>
+        <v>10825</v>
       </c>
       <c r="B107">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C107">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>10825</v>
+        <v>11093</v>
       </c>
       <c r="B108">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C108">
-        <v>13</v>
+        <v>46</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11081</v>
+        <v>11134</v>
       </c>
       <c r="B109">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C109">
         <v>7</v>
@@ -1584,87 +1584,87 @@
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11093</v>
+        <v>11357</v>
       </c>
       <c r="B110">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C110">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11134</v>
+        <v>11492</v>
       </c>
       <c r="B111">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C111">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11357</v>
+        <v>11493</v>
       </c>
       <c r="B112">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C112">
-        <v>55</v>
+        <v>26</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11492</v>
+        <v>11494</v>
       </c>
       <c r="B113">
         <v>1</v>
       </c>
       <c r="C113">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11493</v>
+        <v>11687</v>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C114">
-        <v>26</v>
+        <v>357</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11510</v>
+        <v>11969</v>
       </c>
       <c r="B115">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C115">
-        <v>352</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11886</v>
+        <v>12539</v>
       </c>
       <c r="B116">
         <v>2</v>
       </c>
       <c r="C116">
-        <v>222</v>
+        <v>17</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>11967</v>
+        <v>12608</v>
       </c>
       <c r="B117">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C117">
         <v>7</v>
@@ -1672,7 +1672,7 @@
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>11969</v>
+        <v>12662</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12304</v>
+        <v>12675</v>
       </c>
       <c r="B119">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C119">
         <v>7</v>
@@ -1694,7 +1694,7 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12608</v>
+        <v>12676</v>
       </c>
       <c r="B120">
         <v>3</v>
@@ -1705,43 +1705,43 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12661</v>
+        <v>12677</v>
       </c>
       <c r="B121">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C121">
-        <v>87</v>
+        <v>124</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12662</v>
+        <v>12791</v>
       </c>
       <c r="B122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C122">
-        <v>7</v>
+        <v>465</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12675</v>
+        <v>12870</v>
       </c>
       <c r="B123">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C123">
-        <v>7</v>
+        <v>81</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12676</v>
+        <v>12925</v>
       </c>
       <c r="B124">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C124">
         <v>7</v>
@@ -1749,68 +1749,68 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12677</v>
+        <v>13023</v>
       </c>
       <c r="B125">
         <v>3</v>
       </c>
       <c r="C125">
-        <v>7</v>
+        <v>688</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12791</v>
+        <v>13259</v>
       </c>
       <c r="B126">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C126">
-        <v>468</v>
+        <v>27</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>13023</v>
+        <v>13263</v>
       </c>
       <c r="B127">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C127">
-        <v>342</v>
+        <v>40</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>13034</v>
+        <v>19980</v>
       </c>
       <c r="B128">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C128">
-        <v>684</v>
+        <v>33</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>13263</v>
+        <v>19986</v>
       </c>
       <c r="B129">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C129">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>19986</v>
+        <v>19988</v>
       </c>
       <c r="B130">
         <v>2</v>
       </c>
       <c r="C130">
-        <v>45</v>
+        <v>66</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -1826,13 +1826,13 @@
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>20486</v>
+        <v>20498</v>
       </c>
       <c r="B132">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C132">
-        <v>354</v>
+        <v>114</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -1843,7 +1843,7 @@
         <v>10</v>
       </c>
       <c r="C133">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -1854,138 +1854,160 @@
         <v>7</v>
       </c>
       <c r="C134">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>21454</v>
+        <v>22049</v>
       </c>
       <c r="B135">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C135">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>21793</v>
+        <v>22089</v>
       </c>
       <c r="B136">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C136">
-        <v>374</v>
+        <v>10</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>22049</v>
+        <v>22554</v>
       </c>
       <c r="B137">
         <v>10</v>
       </c>
       <c r="C137">
-        <v>10</v>
+        <v>422</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>22089</v>
+        <v>22565</v>
       </c>
       <c r="B138">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C138">
-        <v>10</v>
+        <v>342</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>22554</v>
+        <v>23235</v>
       </c>
       <c r="B139">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C139">
-        <v>426</v>
+        <v>48</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>23611</v>
+        <v>23494</v>
       </c>
       <c r="B140">
         <v>3</v>
       </c>
       <c r="C140">
-        <v>394</v>
+        <v>125</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>24252</v>
+        <v>23611</v>
       </c>
       <c r="B141">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C141">
-        <v>7</v>
+        <v>394</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>24260</v>
+        <v>24126</v>
       </c>
       <c r="B142">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C142">
-        <v>109</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>24707</v>
+        <v>24127</v>
       </c>
       <c r="B143">
         <v>3</v>
       </c>
       <c r="C143">
-        <v>717</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>25278</v>
+        <v>24252</v>
       </c>
       <c r="B144">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C144">
-        <v>164</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>25286</v>
+        <v>24256</v>
       </c>
       <c r="B145">
         <v>1</v>
       </c>
       <c r="C145">
-        <v>13</v>
+        <v>84</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
+        <v>24707</v>
+      </c>
+      <c r="B146">
+        <v>3</v>
+      </c>
+      <c r="C146">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147">
+        <v>25286</v>
+      </c>
+      <c r="B147">
+        <v>1</v>
+      </c>
+      <c r="C147">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148">
         <v>26103</v>
       </c>
-      <c r="B146">
-        <v>2</v>
-      </c>
-      <c r="C146">
+      <c r="B148">
+        <v>2</v>
+      </c>
+      <c r="C148">
         <v>26</v>
       </c>
     </row>
